--- a/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_ugsc_asitec.xlsx
+++ b/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_ugsc_asitec.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q419"/>
+  <dimension ref="A1:S419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,6 +500,16 @@
       <c r="Q1" t="inlineStr">
         <is>
           <t>ubigeo</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ugel</t>
         </is>
       </c>
     </row>
@@ -567,6 +577,16 @@
           <t>010509</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>UGEL LUYA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -632,6 +652,16 @@
           <t>010509</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>UGEL LUYA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -697,6 +727,16 @@
           <t>010516</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>UGEL LUYA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -762,6 +802,16 @@
           <t>010701</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -827,6 +877,16 @@
           <t>010206</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>UGEL BAGUA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -892,6 +952,16 @@
           <t>010505</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>UGEL LUYA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -957,6 +1027,16 @@
           <t>010312</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>UGEL BONGARÁ</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1022,6 +1102,16 @@
           <t>010201</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>UGEL BAGUA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1087,6 +1177,16 @@
           <t>010705</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1152,6 +1252,16 @@
           <t>010703</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1217,6 +1327,16 @@
           <t>010607</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>UGEL RODRÍGUEZ DE MENDOZA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1282,6 +1402,16 @@
           <t>020607</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1347,6 +1477,16 @@
           <t>020501</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1412,6 +1552,16 @@
           <t>021903</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1477,6 +1627,16 @@
           <t>021006</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1542,6 +1702,16 @@
           <t>030605</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1607,6 +1777,16 @@
           <t>030406</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>UGEL AYMARAES</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1672,6 +1852,16 @@
           <t>030216</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1737,6 +1927,16 @@
           <t>030215</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1802,6 +2002,16 @@
           <t>030712</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>UGEL GRAU</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1867,6 +2077,16 @@
           <t>030708</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>UGEL GRAU</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1932,6 +2152,16 @@
           <t>030604</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1997,6 +2227,16 @@
           <t>030506</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>UGEL COTABAMBAS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2062,6 +2302,16 @@
           <t>030503</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>UGEL COTABAMBAS</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2127,6 +2377,16 @@
           <t>030104</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>UGEL ABANCAY</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2192,6 +2452,16 @@
           <t>030608</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2257,6 +2527,16 @@
           <t>040409</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>UGEL CASTILLA</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2322,6 +2602,16 @@
           <t>040109</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2387,6 +2677,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2452,6 +2752,16 @@
           <t>050114</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2517,6 +2827,16 @@
           <t>050201</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>UGEL CANGALLO</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2582,6 +2902,16 @@
           <t>050506</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2647,6 +2977,16 @@
           <t>050205</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2712,6 +3052,16 @@
           <t>051005</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2777,6 +3127,16 @@
           <t>050412</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2842,6 +3202,16 @@
           <t>050402</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2907,6 +3277,16 @@
           <t>050504</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2972,6 +3352,16 @@
           <t>050617</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3037,6 +3427,16 @@
           <t>050411</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3102,6 +3502,16 @@
           <t>050507</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3167,6 +3577,16 @@
           <t>050102</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3232,6 +3652,16 @@
           <t>050411</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3297,6 +3727,16 @@
           <t>050112</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3362,6 +3802,16 @@
           <t>060610</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3427,6 +3877,16 @@
           <t>060901</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3492,6 +3952,16 @@
           <t>061001</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARCOS</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3557,6 +4027,16 @@
           <t>061101</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>UGEL SAN MIGUEL</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3622,6 +4102,16 @@
           <t>060803</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3687,6 +4177,16 @@
           <t>061306</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>UGEL SANTA CRUZ</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3752,6 +4252,16 @@
           <t>060411</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3817,6 +4327,16 @@
           <t>060611</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3882,6 +4402,16 @@
           <t>060802</t>
         </is>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3949,6 +4479,16 @@
           <t>060103</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4014,6 +4554,16 @@
           <t>060906</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4079,6 +4629,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4144,6 +4704,16 @@
           <t>060601</t>
         </is>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4209,6 +4779,16 @@
           <t>060105</t>
         </is>
       </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4274,6 +4854,16 @@
           <t>060105</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4339,6 +4929,16 @@
           <t>060407</t>
         </is>
       </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4404,6 +5004,16 @@
           <t>060902</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4469,6 +5079,16 @@
           <t>060611</t>
         </is>
       </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4534,6 +5154,16 @@
           <t>061107</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>UGEL SAN MIGUEL</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4599,6 +5229,16 @@
           <t>061301</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>UGEL SANTA CRUZ</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4664,6 +5304,16 @@
           <t>080502</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4729,6 +5379,16 @@
           <t>081104</t>
         </is>
       </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>UGEL PAUCARTAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4794,6 +5454,16 @@
           <t>080804</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4859,6 +5529,16 @@
           <t>080701</t>
         </is>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4924,6 +5604,16 @@
           <t>080705</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4989,6 +5679,16 @@
           <t>080705</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5054,6 +5754,16 @@
           <t>080502</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5119,6 +5829,16 @@
           <t>081208</t>
         </is>
       </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5184,6 +5904,16 @@
           <t>080505</t>
         </is>
       </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5249,6 +5979,16 @@
           <t>080701</t>
         </is>
       </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5314,6 +6054,16 @@
           <t>080502</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5379,6 +6129,16 @@
           <t>080502</t>
         </is>
       </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5444,6 +6204,16 @@
           <t>080701</t>
         </is>
       </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5509,6 +6279,16 @@
           <t>080708</t>
         </is>
       </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5574,6 +6354,16 @@
           <t>080708</t>
         </is>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5639,6 +6429,16 @@
           <t>080704</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5704,6 +6504,16 @@
           <t>080705</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>UGEL CANAS</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5769,6 +6579,16 @@
           <t>081305</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>UGEL URUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5834,6 +6654,16 @@
           <t>080805</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5899,6 +6729,16 @@
           <t>080406</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>UGEL CALCA</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5964,6 +6804,16 @@
           <t>080601</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6029,6 +6879,16 @@
           <t>090717</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>UGEL SURCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6094,6 +6954,16 @@
           <t>090722</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6159,6 +7029,16 @@
           <t>090705</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6224,6 +7104,16 @@
           <t>090201</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>UGEL ACOBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6289,6 +7179,16 @@
           <t>090409</t>
         </is>
       </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>UGEL CASTROVIRREYNA</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6354,6 +7254,16 @@
           <t>090206</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>UGEL ACOBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6419,6 +7329,16 @@
           <t>090716</t>
         </is>
       </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>UGEL SURCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6484,6 +7404,16 @@
           <t>090302</t>
         </is>
       </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6549,6 +7479,16 @@
           <t>090719</t>
         </is>
       </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6614,6 +7554,16 @@
           <t>090119</t>
         </is>
       </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAVELICA</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6679,6 +7629,16 @@
           <t>090207</t>
         </is>
       </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>UGEL ACOBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6744,6 +7704,16 @@
           <t>100104</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6809,6 +7779,16 @@
           <t>100113</t>
         </is>
       </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6874,6 +7854,16 @@
           <t>100103</t>
         </is>
       </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6939,6 +7929,16 @@
           <t>100106</t>
         </is>
       </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7004,6 +8004,16 @@
           <t>100104</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7069,6 +8079,16 @@
           <t>101005</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7134,6 +8154,16 @@
           <t>100704</t>
         </is>
       </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>UGEL MARAÑÓN</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7199,6 +8229,16 @@
           <t>101106</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>UGEL YAROWILCA</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7264,6 +8304,16 @@
           <t>100201</t>
         </is>
       </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>UGEL AMBO</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -7329,6 +8379,16 @@
           <t>101001</t>
         </is>
       </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -7394,6 +8454,16 @@
           <t>100905</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>UGEL PUERTO INCA</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -7459,6 +8529,16 @@
           <t>100603</t>
         </is>
       </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -7524,6 +8604,16 @@
           <t>100203</t>
         </is>
       </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>UGEL AMBO</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7589,6 +8679,16 @@
           <t>100802</t>
         </is>
       </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -7654,6 +8754,16 @@
           <t>100605</t>
         </is>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7719,6 +8829,16 @@
           <t>100104</t>
         </is>
       </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7784,6 +8904,16 @@
           <t>100704</t>
         </is>
       </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>UGEL MARAÑÓN</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7849,6 +8979,16 @@
           <t>100804</t>
         </is>
       </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7914,6 +9054,16 @@
           <t>100602</t>
         </is>
       </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7979,6 +9129,16 @@
           <t>100804</t>
         </is>
       </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -8044,6 +9204,16 @@
           <t>100511</t>
         </is>
       </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>UGEL HUAMALÍES</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -8109,6 +9279,16 @@
           <t>100104</t>
         </is>
       </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -8174,6 +9354,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -8239,6 +9429,16 @@
           <t>100113</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -8304,6 +9504,16 @@
           <t>101001</t>
         </is>
       </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -8369,6 +9579,16 @@
           <t>100902</t>
         </is>
       </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>UGEL PUERTO INCA</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -8434,6 +9654,16 @@
           <t>101106</t>
         </is>
       </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>UGEL YAROWILCA</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -8499,6 +9729,16 @@
           <t>100111</t>
         </is>
       </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -8564,6 +9804,16 @@
           <t>100108</t>
         </is>
       </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -8629,6 +9879,16 @@
           <t>100203</t>
         </is>
       </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>UGEL AMBO</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -8694,6 +9954,16 @@
           <t>120606</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>UGEL PANGOA</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -8759,6 +10029,16 @@
           <t>120606</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>UGEL PANGOA</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8824,6 +10104,16 @@
           <t>120604</t>
         </is>
       </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>UGEL SATIPO</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8889,6 +10179,16 @@
           <t>120132</t>
         </is>
       </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8954,6 +10254,16 @@
           <t>120303</t>
         </is>
       </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>UGEL PICHANAKI</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -9019,6 +10329,16 @@
           <t>120431</t>
         </is>
       </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>UGEL JAUJA</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -9084,6 +10404,16 @@
           <t>120403</t>
         </is>
       </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>UGEL JAUJA</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -9149,6 +10479,16 @@
           <t>120403</t>
         </is>
       </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>UGEL JAUJA</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -9214,6 +10554,16 @@
           <t>120204</t>
         </is>
       </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>UGEL CHUPACA</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -9279,6 +10629,16 @@
           <t>120215</t>
         </is>
       </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>UGEL CONCEPCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -9344,6 +10704,16 @@
           <t>120303</t>
         </is>
       </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>UGEL PICHANAKI</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -9409,6 +10779,16 @@
           <t>120303</t>
         </is>
       </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>UGEL PICHANAKI</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -9474,6 +10854,16 @@
           <t>120303</t>
         </is>
       </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>UGEL PICHANAKI</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -9539,6 +10929,16 @@
           <t>120406</t>
         </is>
       </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>UGEL JAUJA</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -9604,6 +11004,16 @@
           <t>120608</t>
         </is>
       </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -9669,6 +11079,16 @@
           <t>120608</t>
         </is>
       </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -9734,6 +11154,16 @@
           <t>120608</t>
         </is>
       </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -9799,6 +11229,16 @@
           <t>130203</t>
         </is>
       </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -9864,6 +11304,16 @@
           <t>130902</t>
         </is>
       </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -9929,6 +11379,16 @@
           <t>130207</t>
         </is>
       </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -9994,6 +11454,16 @@
           <t>130907</t>
         </is>
       </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -10059,6 +11529,16 @@
           <t>130705</t>
         </is>
       </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>UGEL PACASMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -10124,6 +11604,16 @@
           <t>130604</t>
         </is>
       </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>UGEL OTUZCO</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -10189,6 +11679,16 @@
           <t>131001</t>
         </is>
       </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>UGEL SANTIAGO DE CHUCO</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -10254,6 +11754,16 @@
           <t>130302</t>
         </is>
       </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -10319,6 +11829,16 @@
           <t>130503</t>
         </is>
       </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>UGEL JULCÁN</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -10384,6 +11904,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -10449,6 +11979,16 @@
           <t>130905</t>
         </is>
       </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -10514,6 +12054,16 @@
           <t>130601</t>
         </is>
       </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>UGEL OTUZCO</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -10579,6 +12129,16 @@
           <t>130105</t>
         </is>
       </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -10644,6 +12204,16 @@
           <t>130503</t>
         </is>
       </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>UGEL JULCÁN</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -10709,6 +12279,16 @@
           <t>130604</t>
         </is>
       </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>UGEL OTUZCO</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -10774,6 +12354,16 @@
           <t>130903</t>
         </is>
       </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -10839,6 +12429,16 @@
           <t>130105</t>
         </is>
       </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -10904,6 +12504,16 @@
           <t>130905</t>
         </is>
       </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -10969,6 +12579,16 @@
           <t>140104</t>
         </is>
       </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -11034,6 +12654,16 @@
           <t>140103</t>
         </is>
       </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -11099,6 +12729,16 @@
           <t>140310</t>
         </is>
       </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -11164,6 +12804,16 @@
           <t>140307</t>
         </is>
       </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -11229,6 +12879,16 @@
           <t>140102</t>
         </is>
       </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -11294,6 +12954,16 @@
           <t>150811</t>
         </is>
       </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -11359,6 +13029,16 @@
           <t>160201</t>
         </is>
       </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -11424,6 +13104,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -11489,6 +13179,16 @@
           <t>190106</t>
         </is>
       </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -11554,6 +13254,16 @@
           <t>190203</t>
         </is>
       </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>UGEL DANIEL ALCIDES CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -11619,6 +13329,16 @@
           <t>190109</t>
         </is>
       </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -11684,6 +13404,16 @@
           <t>200303</t>
         </is>
       </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -11749,6 +13479,16 @@
           <t>200303</t>
         </is>
       </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -11814,6 +13554,16 @@
           <t>200406</t>
         </is>
       </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -11879,6 +13629,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -11944,6 +13704,16 @@
           <t>200804</t>
         </is>
       </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -12009,6 +13779,16 @@
           <t>200207</t>
         </is>
       </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -12074,6 +13854,16 @@
           <t>200602</t>
         </is>
       </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -12139,6 +13929,16 @@
           <t>200307</t>
         </is>
       </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -12204,6 +14004,16 @@
           <t>200308</t>
         </is>
       </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -12269,6 +14079,16 @@
           <t>200308</t>
         </is>
       </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -12334,6 +14154,16 @@
           <t>200504</t>
         </is>
       </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>UGEL PAITA</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -12399,6 +14229,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -12464,6 +14304,16 @@
           <t>210310</t>
         </is>
       </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>UGEL CRUCERO</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -12529,6 +14379,16 @@
           <t>210407</t>
         </is>
       </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -12594,6 +14454,16 @@
           <t>210101</t>
         </is>
       </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -12659,6 +14529,16 @@
           <t>211101</t>
         </is>
       </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>UGEL SAN ROMÁN</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -12724,6 +14604,16 @@
           <t>211101</t>
         </is>
       </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>UGEL SAN ROMÁN</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -12789,6 +14679,16 @@
           <t>210204</t>
         </is>
       </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -12854,6 +14754,16 @@
           <t>210709</t>
         </is>
       </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -12919,6 +14829,16 @@
           <t>210201</t>
         </is>
       </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -12984,6 +14904,16 @@
           <t>211206</t>
         </is>
       </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>UGEL SANDIA</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -13049,6 +14979,16 @@
           <t>210709</t>
         </is>
       </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -13114,6 +15054,16 @@
           <t>210808</t>
         </is>
       </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -13179,6 +15129,16 @@
           <t>210204</t>
         </is>
       </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -13244,6 +15204,16 @@
           <t>210102</t>
         </is>
       </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -13309,6 +15279,16 @@
           <t>210806</t>
         </is>
       </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -13374,6 +15354,16 @@
           <t>210407</t>
         </is>
       </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -13439,6 +15429,16 @@
           <t>210102</t>
         </is>
       </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -13504,6 +15504,16 @@
           <t>210209</t>
         </is>
       </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>UGEL CRUCERO</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -13569,6 +15579,16 @@
           <t>211202</t>
         </is>
       </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>UGEL SANDIA</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -13634,6 +15654,16 @@
           <t>210304</t>
         </is>
       </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -13699,6 +15729,16 @@
           <t>210801</t>
         </is>
       </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -13764,6 +15804,16 @@
           <t>210708</t>
         </is>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -13829,6 +15879,16 @@
           <t>210708</t>
         </is>
       </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -13894,6 +15954,16 @@
           <t>210804</t>
         </is>
       </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -13959,6 +16029,16 @@
           <t>210306</t>
         </is>
       </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>UGEL CRUCERO</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -14024,6 +16104,16 @@
           <t>210305</t>
         </is>
       </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -14089,6 +16179,16 @@
           <t>211201</t>
         </is>
       </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>UGEL SANDIA</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -14154,6 +16254,16 @@
           <t>210108</t>
         </is>
       </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -14219,6 +16329,16 @@
           <t>210802</t>
         </is>
       </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -14284,6 +16404,16 @@
           <t>211103</t>
         </is>
       </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>UGEL SAN ROMÁN</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -14349,6 +16479,16 @@
           <t>210602</t>
         </is>
       </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAN</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -14414,6 +16554,16 @@
           <t>210309</t>
         </is>
       </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -14479,6 +16629,16 @@
           <t>210101</t>
         </is>
       </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -14544,6 +16704,16 @@
           <t>211205</t>
         </is>
       </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>UGEL CRUCERO</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -14609,6 +16779,16 @@
           <t>210402</t>
         </is>
       </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -14674,6 +16854,16 @@
           <t>210708</t>
         </is>
       </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -14739,6 +16929,16 @@
           <t>211210</t>
         </is>
       </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>UGEL SANDIA</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -14804,6 +17004,16 @@
           <t>210501</t>
         </is>
       </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>UGEL EL COLLAO</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -14869,6 +17079,16 @@
           <t>210101</t>
         </is>
       </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -14934,6 +17154,16 @@
           <t>211301</t>
         </is>
       </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>UGEL YUNGUYO</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -14999,6 +17229,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -15064,6 +17304,16 @@
           <t>220501</t>
         </is>
       </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>UGEL LAMAS</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -15129,6 +17379,16 @@
           <t>221003</t>
         </is>
       </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -15194,6 +17454,16 @@
           <t>220504</t>
         </is>
       </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>UGEL LAMAS</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -15259,6 +17529,16 @@
           <t>220805</t>
         </is>
       </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -15324,6 +17604,16 @@
           <t>220206</t>
         </is>
       </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>UGEL BELLAVISTA</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -15389,6 +17679,16 @@
           <t>220402</t>
         </is>
       </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>UGEL HUALLAGA</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -15454,6 +17754,16 @@
           <t>220406</t>
         </is>
       </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>UGEL BELLAVISTA</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -15519,6 +17829,16 @@
           <t>221001</t>
         </is>
       </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -15584,6 +17904,16 @@
           <t>250305</t>
         </is>
       </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>UGEL PADRE ABAD</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -15649,6 +17979,16 @@
           <t>030602</t>
         </is>
       </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -15714,6 +18054,16 @@
           <t>050401</t>
         </is>
       </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -15779,6 +18129,16 @@
           <t>021101</t>
         </is>
       </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -15844,6 +18204,16 @@
           <t>190308</t>
         </is>
       </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>UGEL OXAPAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -15909,6 +18279,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -15974,6 +18354,16 @@
           <t>030606</t>
         </is>
       </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -16039,6 +18429,16 @@
           <t>030605</t>
         </is>
       </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -16104,6 +18504,16 @@
           <t>130801</t>
         </is>
       </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>UGEL PATAZ</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -16169,6 +18579,16 @@
           <t>090717</t>
         </is>
       </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>UGEL SURCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -16234,6 +18654,16 @@
           <t>130502</t>
         </is>
       </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>UGEL JULCÁN</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -16299,6 +18729,16 @@
           <t>030606</t>
         </is>
       </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -16364,6 +18804,16 @@
           <t>050116</t>
         </is>
       </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -16429,6 +18879,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -16494,6 +18954,16 @@
           <t>130206</t>
         </is>
       </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -16559,6 +19029,16 @@
           <t>240303</t>
         </is>
       </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>UGEL ZARUMILLA</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -16624,6 +19104,16 @@
           <t>200406</t>
         </is>
       </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -16689,6 +19179,16 @@
           <t>140311</t>
         </is>
       </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -16754,6 +19254,16 @@
           <t>050112</t>
         </is>
       </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -16819,6 +19329,16 @@
           <t>130104</t>
         </is>
       </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>UGEL 03 - TRUJILLO NOR OESTE</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -16884,6 +19404,16 @@
           <t>130206</t>
         </is>
       </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -16949,6 +19479,16 @@
           <t>010704</t>
         </is>
       </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -17014,6 +19554,16 @@
           <t>020606</t>
         </is>
       </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -17079,6 +19629,16 @@
           <t>100607</t>
         </is>
       </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -17144,6 +19704,16 @@
           <t>120201</t>
         </is>
       </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>UGEL CONCEPCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -17209,6 +19779,16 @@
           <t>050701</t>
         </is>
       </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -17274,6 +19854,16 @@
           <t>050403</t>
         </is>
       </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -17339,6 +19929,16 @@
           <t>130601</t>
         </is>
       </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>UGEL OTUZCO</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -17404,6 +20004,16 @@
           <t>060801</t>
         </is>
       </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -17469,6 +20079,16 @@
           <t>200703</t>
         </is>
       </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -17534,6 +20154,16 @@
           <t>020108</t>
         </is>
       </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -17599,6 +20229,16 @@
           <t>211105</t>
         </is>
       </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>UGEL SAN ROMÁN</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -17664,6 +20304,16 @@
           <t>130905</t>
         </is>
       </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -17729,6 +20379,16 @@
           <t>090707</t>
         </is>
       </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>UGEL SURCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -17794,6 +20454,16 @@
           <t>221001</t>
         </is>
       </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -17859,6 +20529,16 @@
           <t>090405</t>
         </is>
       </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>UGEL CASTROVIRREYNA</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -17924,6 +20604,16 @@
           <t>090411</t>
         </is>
       </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAVELICA</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -17989,6 +20679,16 @@
           <t>190112</t>
         </is>
       </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -18054,6 +20754,16 @@
           <t>050708</t>
         </is>
       </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -18119,6 +20829,16 @@
           <t>220807</t>
         </is>
       </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -18184,6 +20904,16 @@
           <t>050407</t>
         </is>
       </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -18249,6 +20979,16 @@
           <t>100601</t>
         </is>
       </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -18314,6 +21054,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -18379,6 +21129,16 @@
           <t>200301</t>
         </is>
       </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -18444,6 +21204,16 @@
           <t>100510</t>
         </is>
       </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>UGEL HUAMALÍES</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -18509,6 +21279,16 @@
           <t>050606</t>
         </is>
       </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -18574,6 +21354,16 @@
           <t>210808</t>
         </is>
       </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -18639,6 +21429,16 @@
           <t>190109</t>
         </is>
       </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -18704,6 +21504,16 @@
           <t>030215</t>
         </is>
       </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -18769,6 +21579,16 @@
           <t>030215</t>
         </is>
       </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -18834,6 +21654,16 @@
           <t>220708</t>
         </is>
       </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>UGEL PICOTA</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -18899,6 +21729,16 @@
           <t>090405</t>
         </is>
       </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>UGEL CASTROVIRREYNA</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -18964,6 +21804,16 @@
           <t>090719</t>
         </is>
       </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -19029,6 +21879,16 @@
           <t>020604</t>
         </is>
       </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -19094,6 +21954,16 @@
           <t>100104</t>
         </is>
       </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -19159,6 +22029,16 @@
           <t>190109</t>
         </is>
       </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -19224,6 +22104,16 @@
           <t>120908</t>
         </is>
       </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>UGEL CHUPACA</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -19289,6 +22179,16 @@
           <t>060906</t>
         </is>
       </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -19354,6 +22254,16 @@
           <t>210205</t>
         </is>
       </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -19419,6 +22329,16 @@
           <t>221001</t>
         </is>
       </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -19484,6 +22404,16 @@
           <t>090511</t>
         </is>
       </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>UGEL CHURCAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -19549,6 +22479,16 @@
           <t>130104</t>
         </is>
       </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>UGEL 03 - TRUJILLO NOR OESTE</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -19614,6 +22554,16 @@
           <t>100603</t>
         </is>
       </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -19679,6 +22629,16 @@
           <t>100605</t>
         </is>
       </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -19744,6 +22704,16 @@
           <t>160201</t>
         </is>
       </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -19809,6 +22779,16 @@
           <t>130902</t>
         </is>
       </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -19874,6 +22854,16 @@
           <t>010515</t>
         </is>
       </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>UGEL LUYA</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -19939,6 +22929,16 @@
           <t>080913</t>
         </is>
       </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -20004,6 +23004,16 @@
           <t>050502</t>
         </is>
       </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -20069,6 +23079,16 @@
           <t>030220</t>
         </is>
       </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -20134,6 +23154,16 @@
           <t>061304</t>
         </is>
       </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>UGEL SANTA CRUZ</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -20199,6 +23229,16 @@
           <t>030704</t>
         </is>
       </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>UGEL GRAU</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -20264,6 +23304,16 @@
           <t>080704</t>
         </is>
       </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -20329,6 +23379,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -20394,6 +23454,16 @@
           <t>220202</t>
         </is>
       </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>UGEL BELLAVISTA</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -20459,6 +23529,16 @@
           <t>010306</t>
         </is>
       </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>UGEL BONGARÁ</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -20524,6 +23604,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -20589,6 +23679,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -20654,6 +23754,16 @@
           <t>080804</t>
         </is>
       </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -20719,6 +23829,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -20784,6 +23904,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -20849,6 +23979,16 @@
           <t>220604</t>
         </is>
       </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL CÁCERES</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -20914,6 +24054,16 @@
           <t>090701</t>
         </is>
       </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -20979,6 +24129,16 @@
           <t>190109</t>
         </is>
       </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -21044,6 +24204,16 @@
           <t>210804</t>
         </is>
       </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -21109,6 +24279,16 @@
           <t>210306</t>
         </is>
       </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>UGEL CRUCERO</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -21174,6 +24354,16 @@
           <t>210206</t>
         </is>
       </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -21239,6 +24429,16 @@
           <t>210208</t>
         </is>
       </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -21304,6 +24504,16 @@
           <t>022003</t>
         </is>
       </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -21369,6 +24579,16 @@
           <t>081307</t>
         </is>
       </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>UGEL URUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -21434,6 +24654,16 @@
           <t>140311</t>
         </is>
       </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -21499,6 +24729,16 @@
           <t>020509</t>
         </is>
       </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -21564,6 +24804,16 @@
           <t>210804</t>
         </is>
       </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -21629,6 +24879,16 @@
           <t>060907</t>
         </is>
       </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -21694,6 +24954,16 @@
           <t>130901</t>
         </is>
       </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -21759,6 +25029,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -21824,6 +25104,16 @@
           <t>211105</t>
         </is>
       </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>UGEL SAN ROMÁN</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -21889,6 +25179,16 @@
           <t>120608</t>
         </is>
       </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>UGEL RIO TAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -21954,6 +25254,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -22019,6 +25329,16 @@
           <t>030701</t>
         </is>
       </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>UGEL GRAU</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -22084,6 +25404,16 @@
           <t>221003</t>
         </is>
       </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -22149,6 +25479,16 @@
           <t>220105</t>
         </is>
       </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>UGEL MOYOBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -22214,6 +25554,16 @@
           <t>110104</t>
         </is>
       </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -22279,6 +25629,16 @@
           <t>060407</t>
         </is>
       </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -22344,6 +25704,16 @@
           <t>060107</t>
         </is>
       </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -22409,6 +25779,16 @@
           <t>220105</t>
         </is>
       </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>UGEL MOYOBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -22474,6 +25854,16 @@
           <t>200408</t>
         </is>
       </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -22539,6 +25929,16 @@
           <t>010522</t>
         </is>
       </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>UGEL LUYA</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -22604,6 +26004,16 @@
           <t>010202</t>
         </is>
       </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>UGEL BAGUA</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -22669,6 +26079,16 @@
           <t>010522</t>
         </is>
       </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>UGEL LUYA</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -22734,6 +26154,16 @@
           <t>021510</t>
         </is>
       </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>UGEL PALLASCA</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -22799,6 +26229,16 @@
           <t>030220</t>
         </is>
       </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -22864,6 +26304,16 @@
           <t>040117</t>
         </is>
       </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -22929,6 +26379,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -22994,6 +26454,16 @@
           <t>050110</t>
         </is>
       </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -23059,6 +26529,16 @@
           <t>050702</t>
         </is>
       </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -23124,6 +26604,16 @@
           <t>060603</t>
         </is>
       </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -23189,6 +26679,16 @@
           <t>080701</t>
         </is>
       </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -23254,6 +26754,16 @@
           <t>080407</t>
         </is>
       </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -23319,6 +26829,16 @@
           <t>080707</t>
         </is>
       </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -23384,6 +26904,16 @@
           <t>081203</t>
         </is>
       </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>UGEL QUISPICANCHI</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -23449,6 +26979,16 @@
           <t>080704</t>
         </is>
       </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -23514,6 +27054,16 @@
           <t>100109</t>
         </is>
       </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -23579,6 +27129,16 @@
           <t>100510</t>
         </is>
       </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>UGEL HUAMALÍES</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -23644,6 +27204,16 @@
           <t>101101</t>
         </is>
       </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>UGEL YAROWILCA</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -23709,6 +27279,16 @@
           <t>100317</t>
         </is>
       </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>UGEL DOS DE MAYO</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -23774,6 +27354,16 @@
           <t>101101</t>
         </is>
       </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>UGEL YAROWILCA</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -23839,6 +27429,16 @@
           <t>100604</t>
         </is>
       </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -23904,6 +27504,16 @@
           <t>100604</t>
         </is>
       </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -23969,6 +27579,16 @@
           <t>100110</t>
         </is>
       </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -24034,6 +27654,16 @@
           <t>130905</t>
         </is>
       </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -24099,6 +27729,16 @@
           <t>150203</t>
         </is>
       </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -24164,6 +27804,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -24229,6 +27879,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -24294,6 +27954,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -24359,6 +28029,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -24424,6 +28104,16 @@
           <t>210708</t>
         </is>
       </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -24489,6 +28179,16 @@
           <t>210202</t>
         </is>
       </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -24554,6 +28254,16 @@
           <t>210204</t>
         </is>
       </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -24619,6 +28329,16 @@
           <t>210404</t>
         </is>
       </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -24684,6 +28404,16 @@
           <t>210205</t>
         </is>
       </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -24749,6 +28479,16 @@
           <t>210404</t>
         </is>
       </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -24814,6 +28554,16 @@
           <t>210204</t>
         </is>
       </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -24879,6 +28629,16 @@
           <t>210206</t>
         </is>
       </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -24944,6 +28704,16 @@
           <t>220501</t>
         </is>
       </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>UGEL LAMAS</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -25009,6 +28779,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -25074,6 +28854,16 @@
           <t>220106</t>
         </is>
       </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>UGEL MOYOBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -25139,6 +28929,16 @@
           <t>220206</t>
         </is>
       </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>UGEL BELLAVISTA</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -25204,6 +29004,16 @@
           <t>250204</t>
         </is>
       </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -25269,6 +29079,16 @@
           <t>211305</t>
         </is>
       </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>UGEL YUNGUYO</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -25334,6 +29154,16 @@
           <t>020112</t>
         </is>
       </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -25399,6 +29229,16 @@
           <t>030201</t>
         </is>
       </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -25464,6 +29304,16 @@
           <t>040107</t>
         </is>
       </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -25529,6 +29379,16 @@
           <t>050405</t>
         </is>
       </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -25594,6 +29454,16 @@
           <t>060407</t>
         </is>
       </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -25659,6 +29529,16 @@
           <t>080302</t>
         </is>
       </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>UGEL ANTA</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -25724,6 +29604,16 @@
           <t>080309</t>
         </is>
       </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>UGEL ANTA</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -25789,6 +29679,16 @@
           <t>081303</t>
         </is>
       </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>UGEL URUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -25854,6 +29754,16 @@
           <t>080501</t>
         </is>
       </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>UGEL CANAS</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -25919,6 +29829,16 @@
           <t>080406</t>
         </is>
       </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>UGEL CALCA</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -25984,6 +29904,16 @@
           <t>090715</t>
         </is>
       </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>UGEL SURCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -26049,6 +29979,16 @@
           <t>090607</t>
         </is>
       </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>UGEL HUAYTARÁ</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -26114,6 +30054,16 @@
           <t>100902</t>
         </is>
       </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>UGEL PUERTO INCA</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -26179,6 +30129,16 @@
           <t>110102</t>
         </is>
       </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -26244,6 +30204,16 @@
           <t>150510</t>
         </is>
       </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -26309,6 +30279,16 @@
           <t>150509</t>
         </is>
       </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -26374,6 +30354,16 @@
           <t>150510</t>
         </is>
       </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -26439,6 +30429,16 @@
           <t>190101</t>
         </is>
       </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -26504,6 +30504,16 @@
           <t>200505</t>
         </is>
       </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>UGEL PAITA</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -26569,6 +30579,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -26634,6 +30654,16 @@
           <t>200505</t>
         </is>
       </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>UGEL PAITA</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -26699,6 +30729,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -26764,6 +30804,16 @@
           <t>200202</t>
         </is>
       </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -26829,6 +30879,16 @@
           <t>210305</t>
         </is>
       </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -26894,6 +30954,16 @@
           <t>210709</t>
         </is>
       </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -26959,6 +31029,16 @@
           <t>210805</t>
         </is>
       </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -27024,6 +31104,16 @@
           <t>210305</t>
         </is>
       </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -27089,6 +31179,16 @@
           <t>210808</t>
         </is>
       </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -27154,6 +31254,16 @@
           <t>210102</t>
         </is>
       </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -27219,6 +31329,16 @@
           <t>210605</t>
         </is>
       </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAN</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -27284,6 +31404,16 @@
           <t>210605</t>
         </is>
       </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAN</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -27349,6 +31479,16 @@
           <t>210402</t>
         </is>
       </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -27414,6 +31554,16 @@
           <t>220801</t>
         </is>
       </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -27479,6 +31629,16 @@
           <t>220605</t>
         </is>
       </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL CÁCERES</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -27544,6 +31704,16 @@
           <t>220804</t>
         </is>
       </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -27609,6 +31779,16 @@
           <t>220801</t>
         </is>
       </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -27674,6 +31854,16 @@
           <t>240104</t>
         </is>
       </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_ugsc_asitec.xlsx
+++ b/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_ugsc_asitec.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S419"/>
+  <dimension ref="A1:T419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +510,11 @@
       <c r="S1" t="inlineStr">
         <is>
           <t>ugel</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>fuente</t>
         </is>
       </c>
     </row>
@@ -587,6 +592,11 @@
           <t>UGEL LUYA</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -662,6 +672,11 @@
           <t>UGEL LUYA</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -737,6 +752,11 @@
           <t>UGEL LUYA</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -812,6 +832,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -887,6 +912,11 @@
           <t>UGEL BAGUA</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -962,6 +992,11 @@
           <t>UGEL LUYA</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1037,6 +1072,11 @@
           <t>UGEL BONGARÁ</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1112,6 +1152,11 @@
           <t>UGEL BAGUA</t>
         </is>
       </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1187,6 +1232,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1262,6 +1312,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1337,6 +1392,11 @@
           <t>UGEL RODRÍGUEZ DE MENDOZA</t>
         </is>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1412,6 +1472,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1487,6 +1552,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1562,6 +1632,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1637,6 +1712,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1712,6 +1792,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1787,6 +1872,11 @@
           <t>UGEL AYMARAES</t>
         </is>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1862,6 +1952,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1937,6 +2032,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2012,6 +2112,11 @@
           <t>UGEL GRAU</t>
         </is>
       </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2087,6 +2192,11 @@
           <t>UGEL GRAU</t>
         </is>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2162,6 +2272,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2237,6 +2352,11 @@
           <t>UGEL COTABAMBAS</t>
         </is>
       </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2312,6 +2432,11 @@
           <t>UGEL COTABAMBAS</t>
         </is>
       </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2387,6 +2512,11 @@
           <t>UGEL ABANCAY</t>
         </is>
       </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2462,6 +2592,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2537,6 +2672,11 @@
           <t>UGEL CASTILLA</t>
         </is>
       </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2612,6 +2752,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2687,6 +2832,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2762,6 +2912,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2837,6 +2992,11 @@
           <t>UGEL CANGALLO</t>
         </is>
       </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2912,6 +3072,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2987,6 +3152,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3062,6 +3232,11 @@
           <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3137,6 +3312,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3212,6 +3392,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3287,6 +3472,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3362,6 +3552,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3437,6 +3632,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3512,6 +3712,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3587,6 +3792,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3662,6 +3872,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3737,6 +3952,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3812,6 +4032,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3887,6 +4112,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3962,6 +4192,11 @@
           <t>UGEL SAN MARCOS</t>
         </is>
       </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4037,6 +4272,11 @@
           <t>UGEL SAN MIGUEL</t>
         </is>
       </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4112,6 +4352,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4187,6 +4432,11 @@
           <t>UGEL SANTA CRUZ</t>
         </is>
       </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4262,6 +4512,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4337,6 +4592,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4412,6 +4672,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4489,6 +4754,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4564,6 +4834,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4639,6 +4914,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4714,6 +4994,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4789,6 +5074,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4864,6 +5154,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4939,6 +5234,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5014,6 +5314,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5089,6 +5394,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5164,6 +5474,11 @@
           <t>UGEL SAN MIGUEL</t>
         </is>
       </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5239,6 +5554,11 @@
           <t>UGEL SANTA CRUZ</t>
         </is>
       </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5314,6 +5634,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5389,6 +5714,11 @@
           <t>UGEL PAUCARTAMBO</t>
         </is>
       </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5464,6 +5794,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5539,6 +5874,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5614,6 +5954,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5689,6 +6034,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5764,6 +6114,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5839,6 +6194,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5914,6 +6274,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5989,6 +6354,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6064,6 +6434,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6139,6 +6514,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6214,6 +6594,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6289,6 +6674,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6364,6 +6754,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6439,6 +6834,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6514,6 +6914,11 @@
           <t>UGEL CANAS</t>
         </is>
       </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6589,6 +6994,11 @@
           <t>UGEL URUBAMBA</t>
         </is>
       </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6664,6 +7074,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6739,6 +7154,11 @@
           <t>UGEL CALCA</t>
         </is>
       </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6814,6 +7234,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6889,6 +7314,11 @@
           <t>UGEL SURCUBAMBA</t>
         </is>
       </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6964,6 +7394,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7039,6 +7474,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7114,6 +7554,11 @@
           <t>UGEL ACOBAMBA</t>
         </is>
       </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7189,6 +7634,11 @@
           <t>UGEL CASTROVIRREYNA</t>
         </is>
       </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7264,6 +7714,11 @@
           <t>UGEL ACOBAMBA</t>
         </is>
       </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7339,6 +7794,11 @@
           <t>UGEL SURCUBAMBA</t>
         </is>
       </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7414,6 +7874,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7489,6 +7954,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7564,6 +8034,11 @@
           <t>UGEL HUANCAVELICA</t>
         </is>
       </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7639,6 +8114,11 @@
           <t>UGEL ACOBAMBA</t>
         </is>
       </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7714,6 +8194,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7789,6 +8274,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7864,6 +8354,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7939,6 +8434,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8014,6 +8514,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8089,6 +8594,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8164,6 +8674,11 @@
           <t>UGEL MARAÑÓN</t>
         </is>
       </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8239,6 +8754,11 @@
           <t>UGEL YAROWILCA</t>
         </is>
       </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8314,6 +8834,11 @@
           <t>UGEL AMBO</t>
         </is>
       </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8389,6 +8914,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8464,6 +8994,11 @@
           <t>UGEL PUERTO INCA</t>
         </is>
       </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8539,6 +9074,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -8614,6 +9154,11 @@
           <t>UGEL AMBO</t>
         </is>
       </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -8689,6 +9234,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8764,6 +9314,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8839,6 +9394,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8914,6 +9474,11 @@
           <t>UGEL MARAÑÓN</t>
         </is>
       </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8989,6 +9554,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9064,6 +9634,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -9139,6 +9714,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9214,6 +9794,11 @@
           <t>UGEL HUAMALÍES</t>
         </is>
       </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9289,6 +9874,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -9364,6 +9954,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9439,6 +10034,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9514,6 +10114,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -9589,6 +10194,11 @@
           <t>UGEL PUERTO INCA</t>
         </is>
       </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -9664,6 +10274,11 @@
           <t>UGEL YAROWILCA</t>
         </is>
       </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -9739,6 +10354,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -9814,6 +10434,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -9889,6 +10514,11 @@
           <t>UGEL AMBO</t>
         </is>
       </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -9964,6 +10594,11 @@
           <t>UGEL PANGOA</t>
         </is>
       </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -10039,6 +10674,11 @@
           <t>UGEL PANGOA</t>
         </is>
       </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -10114,6 +10754,11 @@
           <t>UGEL SATIPO</t>
         </is>
       </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -10189,6 +10834,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -10264,6 +10914,11 @@
           <t>UGEL PICHANAKI</t>
         </is>
       </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -10339,6 +10994,11 @@
           <t>UGEL JAUJA</t>
         </is>
       </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -10414,6 +11074,11 @@
           <t>UGEL JAUJA</t>
         </is>
       </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10489,6 +11154,11 @@
           <t>UGEL JAUJA</t>
         </is>
       </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10564,6 +11234,11 @@
           <t>UGEL CHUPACA</t>
         </is>
       </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10639,6 +11314,11 @@
           <t>UGEL CONCEPCIÓN</t>
         </is>
       </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10714,6 +11394,11 @@
           <t>UGEL PICHANAKI</t>
         </is>
       </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -10789,6 +11474,11 @@
           <t>UGEL PICHANAKI</t>
         </is>
       </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -10864,6 +11554,11 @@
           <t>UGEL PICHANAKI</t>
         </is>
       </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -10939,6 +11634,11 @@
           <t>UGEL JAUJA</t>
         </is>
       </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -11014,6 +11714,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -11089,6 +11794,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -11164,6 +11874,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -11239,6 +11954,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -11314,6 +12034,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -11389,6 +12114,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -11464,6 +12194,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -11539,6 +12274,11 @@
           <t>UGEL PACASMAYO</t>
         </is>
       </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -11614,6 +12354,11 @@
           <t>UGEL OTUZCO</t>
         </is>
       </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -11689,6 +12434,11 @@
           <t>UGEL SANTIAGO DE CHUCO</t>
         </is>
       </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -11764,6 +12514,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -11839,6 +12594,11 @@
           <t>UGEL JULCÁN</t>
         </is>
       </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -11914,6 +12674,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -11989,6 +12754,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -12064,6 +12834,11 @@
           <t>UGEL OTUZCO</t>
         </is>
       </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -12139,6 +12914,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -12214,6 +12994,11 @@
           <t>UGEL JULCÁN</t>
         </is>
       </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -12289,6 +13074,11 @@
           <t>UGEL OTUZCO</t>
         </is>
       </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -12364,6 +13154,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -12439,6 +13234,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -12514,6 +13314,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -12589,6 +13394,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -12664,6 +13474,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -12739,6 +13554,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -12814,6 +13634,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -12889,6 +13714,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -12964,6 +13794,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -13039,6 +13874,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -13114,6 +13954,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -13189,6 +14034,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -13264,6 +14114,11 @@
           <t>UGEL DANIEL ALCIDES CARRIÓN</t>
         </is>
       </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -13339,6 +14194,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -13414,6 +14274,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -13489,6 +14354,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -13564,6 +14434,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -13639,6 +14514,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -13714,6 +14594,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -13789,6 +14674,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -13864,6 +14754,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -13939,6 +14834,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -14014,6 +14914,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -14089,6 +14994,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -14164,6 +15074,11 @@
           <t>UGEL PAITA</t>
         </is>
       </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -14239,6 +15154,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -14314,6 +15234,11 @@
           <t>UGEL CRUCERO</t>
         </is>
       </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -14389,6 +15314,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -14464,6 +15394,11 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -14539,6 +15474,11 @@
           <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -14614,6 +15554,11 @@
           <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -14689,6 +15634,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -14764,6 +15714,11 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -14839,6 +15794,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -14914,6 +15874,11 @@
           <t>UGEL SANDIA</t>
         </is>
       </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -14989,6 +15954,11 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -15064,6 +16034,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -15139,6 +16114,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -15214,6 +16194,11 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -15289,6 +16274,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -15364,6 +16354,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -15439,6 +16434,11 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -15514,6 +16514,11 @@
           <t>UGEL CRUCERO</t>
         </is>
       </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -15589,6 +16594,11 @@
           <t>UGEL SANDIA</t>
         </is>
       </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -15664,6 +16674,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -15739,6 +16754,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -15814,6 +16834,11 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -15889,6 +16914,11 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -15964,6 +16994,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -16039,6 +17074,11 @@
           <t>UGEL CRUCERO</t>
         </is>
       </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -16114,6 +17154,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -16189,6 +17234,11 @@
           <t>UGEL SANDIA</t>
         </is>
       </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -16264,6 +17314,11 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -16339,6 +17394,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -16414,6 +17474,11 @@
           <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -16489,6 +17554,11 @@
           <t>UGEL HUANCAN</t>
         </is>
       </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -16564,6 +17634,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -16639,6 +17714,11 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -16714,6 +17794,11 @@
           <t>UGEL CRUCERO</t>
         </is>
       </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -16789,6 +17874,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -16864,6 +17954,11 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -16939,6 +18034,11 @@
           <t>UGEL SANDIA</t>
         </is>
       </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -17014,6 +18114,11 @@
           <t>UGEL EL COLLAO</t>
         </is>
       </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -17089,6 +18194,11 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -17164,6 +18274,11 @@
           <t>UGEL YUNGUYO</t>
         </is>
       </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -17239,6 +18354,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -17314,6 +18434,11 @@
           <t>UGEL LAMAS</t>
         </is>
       </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -17389,6 +18514,11 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -17464,6 +18594,11 @@
           <t>UGEL LAMAS</t>
         </is>
       </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -17539,6 +18674,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -17614,6 +18754,11 @@
           <t>UGEL BELLAVISTA</t>
         </is>
       </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -17689,6 +18834,11 @@
           <t>UGEL HUALLAGA</t>
         </is>
       </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -17764,6 +18914,11 @@
           <t>UGEL BELLAVISTA</t>
         </is>
       </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -17839,6 +18994,11 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -17914,6 +19074,11 @@
           <t>UGEL PADRE ABAD</t>
         </is>
       </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -17989,6 +19154,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -18064,6 +19234,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -18139,6 +19314,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -18214,6 +19394,11 @@
           <t>UGEL OXAPAMPA</t>
         </is>
       </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -18289,6 +19474,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -18364,6 +19554,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -18439,6 +19634,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -18514,6 +19714,11 @@
           <t>UGEL PATAZ</t>
         </is>
       </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -18589,6 +19794,11 @@
           <t>UGEL SURCUBAMBA</t>
         </is>
       </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -18664,6 +19874,11 @@
           <t>UGEL JULCÁN</t>
         </is>
       </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -18739,6 +19954,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -18814,6 +20034,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -18889,6 +20114,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -18964,6 +20194,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -19039,6 +20274,11 @@
           <t>UGEL ZARUMILLA</t>
         </is>
       </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -19114,6 +20354,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -19189,6 +20434,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -19264,6 +20514,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -19339,6 +20594,11 @@
           <t>UGEL 03 - TRUJILLO NOR OESTE</t>
         </is>
       </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -19414,6 +20674,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -19489,6 +20754,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -19564,6 +20834,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -19639,6 +20914,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -19714,6 +20994,11 @@
           <t>UGEL CONCEPCIÓN</t>
         </is>
       </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -19789,6 +21074,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -19864,6 +21154,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -19939,6 +21234,11 @@
           <t>UGEL OTUZCO</t>
         </is>
       </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -20014,6 +21314,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -20089,6 +21394,11 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -20164,6 +21474,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -20239,6 +21554,11 @@
           <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -20314,6 +21634,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -20389,6 +21714,11 @@
           <t>UGEL SURCUBAMBA</t>
         </is>
       </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -20464,6 +21794,11 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -20539,6 +21874,11 @@
           <t>UGEL CASTROVIRREYNA</t>
         </is>
       </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -20614,6 +21954,11 @@
           <t>UGEL HUANCAVELICA</t>
         </is>
       </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -20689,6 +22034,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -20764,6 +22114,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -20839,6 +22194,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -20914,6 +22274,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -20989,6 +22354,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -21064,6 +22434,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -21139,6 +22514,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -21214,6 +22594,11 @@
           <t>UGEL HUAMALÍES</t>
         </is>
       </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -21289,6 +22674,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -21364,6 +22754,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -21439,6 +22834,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -21514,6 +22914,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -21589,6 +22994,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -21664,6 +23074,11 @@
           <t>UGEL PICOTA</t>
         </is>
       </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -21739,6 +23154,11 @@
           <t>UGEL CASTROVIRREYNA</t>
         </is>
       </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -21814,6 +23234,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -21889,6 +23314,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -21964,6 +23394,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -22039,6 +23474,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -22114,6 +23554,11 @@
           <t>UGEL CHUPACA</t>
         </is>
       </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -22189,6 +23634,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -22264,6 +23714,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -22339,6 +23794,11 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -22414,6 +23874,11 @@
           <t>UGEL CHURCAMPA</t>
         </is>
       </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -22489,6 +23954,11 @@
           <t>UGEL 03 - TRUJILLO NOR OESTE</t>
         </is>
       </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -22564,6 +24034,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -22639,6 +24114,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -22714,6 +24194,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -22789,6 +24274,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -22864,6 +24354,11 @@
           <t>UGEL LUYA</t>
         </is>
       </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -22939,6 +24434,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -23014,6 +24514,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -23089,6 +24594,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -23164,6 +24674,11 @@
           <t>UGEL SANTA CRUZ</t>
         </is>
       </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -23239,6 +24754,11 @@
           <t>UGEL GRAU</t>
         </is>
       </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -23314,6 +24834,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -23389,6 +24914,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -23464,6 +24994,11 @@
           <t>UGEL BELLAVISTA</t>
         </is>
       </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -23539,6 +25074,11 @@
           <t>UGEL BONGARÁ</t>
         </is>
       </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -23614,6 +25154,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -23689,6 +25234,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -23764,6 +25314,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -23839,6 +25394,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -23914,6 +25474,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -23989,6 +25554,11 @@
           <t>UGEL MARISCAL CÁCERES</t>
         </is>
       </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -24064,6 +25634,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -24139,6 +25714,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -24214,6 +25794,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -24289,6 +25874,11 @@
           <t>UGEL CRUCERO</t>
         </is>
       </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -24364,6 +25954,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -24439,6 +26034,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -24514,6 +26114,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -24589,6 +26194,11 @@
           <t>UGEL URUBAMBA</t>
         </is>
       </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -24664,6 +26274,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -24739,6 +26354,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -24814,6 +26434,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -24889,6 +26514,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -24964,6 +26594,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -25039,6 +26674,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -25114,6 +26754,11 @@
           <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -25189,6 +26834,11 @@
           <t>UGEL RIO TAMBO</t>
         </is>
       </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -25264,6 +26914,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -25339,6 +26994,11 @@
           <t>UGEL GRAU</t>
         </is>
       </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -25414,6 +27074,11 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -25489,6 +27154,11 @@
           <t>UGEL MOYOBAMBA</t>
         </is>
       </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -25564,6 +27234,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -25639,6 +27314,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -25714,6 +27394,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -25789,6 +27474,11 @@
           <t>UGEL MOYOBAMBA</t>
         </is>
       </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -25864,6 +27554,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -25939,6 +27634,11 @@
           <t>UGEL LUYA</t>
         </is>
       </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -26014,6 +27714,11 @@
           <t>UGEL BAGUA</t>
         </is>
       </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -26089,6 +27794,11 @@
           <t>UGEL LUYA</t>
         </is>
       </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -26164,6 +27874,11 @@
           <t>UGEL PALLASCA</t>
         </is>
       </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -26239,6 +27954,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -26314,6 +28034,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -26389,6 +28114,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -26464,6 +28194,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -26539,6 +28274,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -26614,6 +28354,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -26689,6 +28434,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -26764,6 +28514,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -26839,6 +28594,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -26914,6 +28674,11 @@
           <t>UGEL QUISPICANCHI</t>
         </is>
       </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -26989,6 +28754,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -27064,6 +28834,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -27139,6 +28914,11 @@
           <t>UGEL HUAMALÍES</t>
         </is>
       </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -27214,6 +28994,11 @@
           <t>UGEL YAROWILCA</t>
         </is>
       </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -27289,6 +29074,11 @@
           <t>UGEL DOS DE MAYO</t>
         </is>
       </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -27364,6 +29154,11 @@
           <t>UGEL YAROWILCA</t>
         </is>
       </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -27439,6 +29234,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -27514,6 +29314,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -27589,6 +29394,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -27664,6 +29474,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -27739,6 +29554,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -27814,6 +29634,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -27889,6 +29714,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -27964,6 +29794,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -28039,6 +29874,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -28114,6 +29954,11 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -28189,6 +30034,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -28264,6 +30114,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -28339,6 +30194,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -28414,6 +30274,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -28489,6 +30354,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -28564,6 +30434,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -28639,6 +30514,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -28714,6 +30594,11 @@
           <t>UGEL LAMAS</t>
         </is>
       </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -28789,6 +30674,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -28864,6 +30754,11 @@
           <t>UGEL MOYOBAMBA</t>
         </is>
       </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -28939,6 +30834,11 @@
           <t>UGEL BELLAVISTA</t>
         </is>
       </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -29014,6 +30914,11 @@
           <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -29089,6 +30994,11 @@
           <t>UGEL YUNGUYO</t>
         </is>
       </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -29164,6 +31074,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -29239,6 +31154,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -29314,6 +31234,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -29389,6 +31314,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -29464,6 +31394,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -29539,6 +31474,11 @@
           <t>UGEL ANTA</t>
         </is>
       </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -29614,6 +31554,11 @@
           <t>UGEL ANTA</t>
         </is>
       </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -29689,6 +31634,11 @@
           <t>UGEL URUBAMBA</t>
         </is>
       </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -29764,6 +31714,11 @@
           <t>UGEL CANAS</t>
         </is>
       </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -29839,6 +31794,11 @@
           <t>UGEL CALCA</t>
         </is>
       </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -29914,6 +31874,11 @@
           <t>UGEL SURCUBAMBA</t>
         </is>
       </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -29989,6 +31954,11 @@
           <t>UGEL HUAYTARÁ</t>
         </is>
       </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -30064,6 +32034,11 @@
           <t>UGEL PUERTO INCA</t>
         </is>
       </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -30139,6 +32114,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -30214,6 +32194,11 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -30289,6 +32274,11 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -30364,6 +32354,11 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -30439,6 +32434,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -30514,6 +32514,11 @@
           <t>UGEL PAITA</t>
         </is>
       </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -30589,6 +32594,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -30664,6 +32674,11 @@
           <t>UGEL PAITA</t>
         </is>
       </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -30739,6 +32754,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -30814,6 +32834,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -30889,6 +32914,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -30964,6 +32994,11 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -31039,6 +33074,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -31114,6 +33154,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -31189,6 +33234,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -31264,6 +33314,11 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -31339,6 +33394,11 @@
           <t>UGEL HUANCAN</t>
         </is>
       </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -31414,6 +33474,11 @@
           <t>UGEL HUANCAN</t>
         </is>
       </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -31489,6 +33554,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -31564,6 +33634,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -31639,6 +33714,11 @@
           <t>UGEL MARISCAL CÁCERES</t>
         </is>
       </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -31714,6 +33794,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -31789,6 +33874,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -31864,6 +33954,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_ugsc_asitec.xlsx
+++ b/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_ugsc_asitec.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T419"/>
+  <dimension ref="A1:V419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,6 +513,16 @@
         </is>
       </c>
       <c r="T1" t="inlineStr">
+        <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -594,6 +604,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>18132 JOSE ANTONIO ENCINAS FRANCO</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -674,6 +694,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>RAMON CASTILLA</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -754,6 +784,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -834,6 +874,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>16683 ANTONIO JOSMEL PASTOR MUÑOZ/16683 ANTONIO JOSMEL PASTOR MUÑOZ</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -914,6 +964,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE GUADALUPE FE Y ALEGRIA 31/NUESTRA SEÑORA DE GUADALUPE FE Y ALEGRIA 31/NUESTRA SEÑORA DE GUADALUPE FE Y ALEGRIA 31/NUESTRA SEÑORA DE GUADALUPE FE Y ALEGRIA 31/NUESTRA SEÑORA DE GUADALUPE FE Y ALEGRIA 31</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -994,6 +1054,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
+          <t>MANUEL GONZALES PRADA</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1074,6 +1144,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1154,6 +1234,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
+          <t>LA INMACULADA/LA INMACULADA/LA INMACULADA</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1234,6 +1324,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>VIRGEN DE LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1314,6 +1414,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>SAN PABLO</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1394,6 +1504,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>VIRGEN DEL CARMEN/VIRGEN DEL CARMEN/18240</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1474,6 +1594,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>86284 APOSTOL SANTIAGO/86284 APOSTOL SANTIAGO</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1554,6 +1684,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
+          <t>86214 GUILLERMO BRACALE RAMOS/86214 GUILLERMO BRACALE RAMOS</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1634,6 +1774,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
+          <t>IGNACIO CASTILLO SOTOMAYOR</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1714,6 +1864,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
+          <t>86951-1</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1794,6 +1954,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1874,6 +2044,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>54310 LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1954,6 +2134,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
+          <t>54221</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2034,6 +2224,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
+          <t>SANTA MARIA DE CHICMO/54210</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2114,6 +2314,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
+          <t>JOSE ANTONIO ENCINAS FRANCO</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2194,6 +2404,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
+          <t>SAN MARCOS/54636</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2274,6 +2494,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
+          <t>RAMIRO PRIALE PRIALE/JOSE MARIA FLORES/RAMIRO PRIALE PRIALE</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2354,6 +2584,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2434,6 +2674,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
+          <t>CEMA ÑAHUINLLA</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2514,6 +2764,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
+          <t>54054</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2594,6 +2854,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
+          <t>54198</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2674,6 +2944,16 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
+          <t>40324 JOSE MIGUEL MORALES DASSO</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2754,6 +3034,16 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
+          <t>41030 EDUARDO LOPEZ DE ROMAÑA/41030 EDUARDO LOPEZ DE ROMAÑA</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2834,6 +3124,16 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
+          <t>40157 JORGE LUIS BORGES</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2914,6 +3214,16 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
+          <t>JOSE DE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2994,6 +3304,16 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
+          <t>JACINTO PRADO PILLACA/38124</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3074,6 +3394,16 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
+          <t>ROSASPAMPA/ROSASPAMPA/ROSASPAMPA</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3154,6 +3484,16 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
+          <t>414-5</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3234,6 +3574,16 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
+          <t>FERNANDO BELAUNDE TERRY</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3314,6 +3664,16 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
+          <t>38348</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3394,6 +3754,16 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
+          <t>38320</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3474,6 +3844,16 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
+          <t>38375</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3554,6 +3934,16 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
+          <t>AGROPECUARIO SAN PABLO</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3634,6 +4024,16 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
+          <t>SAN JOSE BENDEZU</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3714,6 +4114,16 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
+          <t>38994-2</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3794,6 +4204,16 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
+          <t>38587</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3874,6 +4294,16 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
+          <t>JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3954,6 +4384,16 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
+          <t>SAN CRISTOBAL</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4034,6 +4474,16 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
+          <t>10359</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4114,6 +4564,16 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
+          <t>16631/16631</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4194,6 +4654,16 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
+          <t>82236</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4274,6 +4744,16 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
+          <t>82773/82773</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4354,6 +4834,16 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4434,6 +4924,16 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
+          <t>10675</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4514,6 +5014,16 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
+          <t>498/SAGRADO CORAZON DE JESUS/101000 HNO. FELIX MONTENEGRO ZULOETA</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4594,6 +5104,16 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
+          <t>CRUZ DE CHALPON</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4674,6 +5194,16 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
+          <t>16012 JOSE CARRION PAZ/16012 JOSE CARRION PAZ</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4756,6 +5286,16 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
+          <t>82892/82892</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4836,6 +5376,16 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
+          <t>16979/16979</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4916,6 +5466,16 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
+          <t>AGROPECUARIO CHUQUIBAMBA</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4996,6 +5556,16 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
+          <t>16973</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5076,6 +5646,16 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
+          <t>82161</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5156,6 +5736,16 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
+          <t>SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5236,6 +5826,16 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
+          <t>JORGE BASADRE</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5316,6 +5916,16 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
+          <t>16374</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5396,6 +6006,16 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
+          <t>TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5476,6 +6096,16 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
+          <t>SAN ANDRES</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5556,6 +6186,16 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
+          <t>INDOAMERICANO</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5636,6 +6276,16 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
+          <t>CESAR VALLEJO/537/56128</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5716,6 +6366,16 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
+          <t>50455/50455</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5796,6 +6456,16 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
+          <t>JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5876,6 +6546,16 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
+          <t>57004 ROSA DE AMERICA/57004 ROSA DE AMERICA/57004 ROSA DE AMERICA</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5956,6 +6636,16 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6036,6 +6726,16 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
+          <t>56286/56286/56286</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6116,6 +6816,16 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
+          <t>56160/ALTIVA CANAS/56160</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6196,6 +6906,16 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
+          <t>27 DE NOVIEMBRE</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6276,6 +6996,16 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6356,6 +7086,16 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
+          <t>56248</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6436,6 +7176,16 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
+          <t>56160/ALTIVA CANAS/56160</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6516,6 +7266,16 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
+          <t>INTEQ KANCHAN</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6596,6 +7356,16 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
+          <t>56315/56315/56315</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6676,6 +7446,16 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
+          <t>56304</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6756,6 +7536,16 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6836,6 +7626,16 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
+          <t>ARMIRI/ARMIRI/ARMIRI</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6916,6 +7716,16 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
+          <t>56284/56284</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6996,6 +7806,16 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
+          <t>ANTONIO SINCHIRROCA</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7076,6 +7896,16 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7156,6 +7986,16 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
+          <t>CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7236,6 +8076,16 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
+          <t>1233/56006 GAONA CISNEROS/56006 GAONA CISNEROS</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7316,6 +8166,16 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
+          <t>31278</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7396,6 +8256,16 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7476,6 +8346,16 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7556,6 +8436,16 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
+          <t>SERGIO QUIJADA JARA</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7636,6 +8526,16 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
+          <t>CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7716,6 +8616,16 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
+          <t>36170 MI PERU</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7796,6 +8706,16 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
+          <t>JUAN VELAZCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7876,6 +8796,16 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
+          <t>36299</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7956,6 +8886,16 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
+          <t>31330</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8036,6 +8976,16 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
+          <t>36089</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8116,6 +9066,16 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8196,6 +9156,16 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
+          <t>32023 MARINO SILVA GOMEZ/32023 MARINO SILVA GOMEZ/32023 MARINO SILVA GOMEZ</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8276,6 +9246,16 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
+          <t>32070/32070</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8356,6 +9336,16 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LOURDES/NUESTRA SEÑORA DE LOURDES</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8436,6 +9426,16 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
+          <t>33076 PEDRO VILCA APAZA/33076 PEDRO VILCA APAZA/33076 PEDRO VILCA APAZA</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8516,6 +9516,16 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
+          <t>32995/32995/32995</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8596,6 +9606,16 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
+          <t>MICAELA BASTIDAS PUYUCAHUA/MICAELA BASTIDAS PUYUCAHUA</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8676,6 +9696,16 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
+          <t>33404/33404</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8756,6 +9786,16 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
+          <t>32231 HIPOLITO UNANUE/32231 HIPOLITO UNANUE</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8836,6 +9876,16 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
+          <t>32644/32644</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8916,6 +9966,16 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8996,6 +10056,16 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
+          <t>32986/32986</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9076,6 +10146,16 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
+          <t>CEPPAT RIO AZUL/CEPPAT RIO AZUL</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9156,6 +10236,16 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
+          <t>32146/32146</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9236,6 +10326,16 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
+          <t>32608/32608/32608</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9316,6 +10416,16 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
+          <t>AGROPECUARIO BOLAINA/AGROPECUARIO BOLAINA/AGROPECUARIO BOLAINA</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9396,6 +10506,16 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
+          <t>32080 CARLOS CASTILLO RIOS/32080 CARLOS CASTILLO RIOS</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9476,6 +10596,16 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
+          <t>32751/32751</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9556,6 +10686,16 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
+          <t>32625</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9636,6 +10776,16 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
+          <t>PUMAHUASI/PUMAHUASI</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9716,6 +10866,16 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
+          <t>GOYAR PUNTA/33301/33301</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9796,6 +10956,16 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
+          <t>32421/32421</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9876,6 +11046,16 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
+          <t>32819/32819</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9956,6 +11136,16 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
+          <t>32729</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10036,6 +11226,16 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
+          <t>32692/32692/32692</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10116,6 +11316,16 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
+          <t>JOSE VARALLANOS</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10196,6 +11406,16 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
+          <t>33412 LAZARO FLORIDA SCHMIDT</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10276,6 +11496,16 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
+          <t>32233 MIGUEL GRAU/32233 MIGUEL GRAU/32233 MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10356,6 +11586,16 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
+          <t>MARIO VARGAS LLOSA/MARIO VARGAS LLOSA/MARIO VARGAS LLOSA</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10436,6 +11676,16 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
+          <t>32117/32117</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10516,6 +11766,16 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
+          <t>32177 JOSE PEDRO CASTILLO TERRONES/32177 JOSE PEDRO CASTILLO TERRONES</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10596,6 +11856,16 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
+          <t>SAN MARTIN/SAN MARTIN/SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10676,6 +11946,16 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
+          <t>CAMPIRUSHARI</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10756,6 +12036,16 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
+          <t>GENERAL RAFAEL HOYOS RUBIO/GENERAL RAFAEL HOYOS RUBIO/GENERAL RAFAEL HOYOS RUBIO</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10836,6 +12126,16 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
+          <t>COMANDANTE PNP HORACIO PATIÑO CRUZATTI</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10916,6 +12216,16 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
+          <t>MANUEL GONZALES PRADA/MANUEL GONZALES PRADA/MANUEL GONZALES PRADA/MANUEL GONZALES PRADA</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10996,6 +12306,16 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
+          <t>30532 HEROES DE LA BREÑA/30532 HEROES DE LA BREÑA/30532 HEROES DE LA BREÑA</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11076,6 +12396,16 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
+          <t>1512 NUESTRA SEÑORA DE COCHARCAS</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11156,6 +12486,16 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
+          <t>LIBERTADOR RAMON CASTILLA</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11236,6 +12576,16 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
+          <t>SAN ROQUE</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11316,6 +12666,16 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
+          <t>FRANCISCANA PADRE PIO SAROBE/FRANCISCANA PADRE PIO SAROBE</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11396,6 +12756,16 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
+          <t>POLITECNICO SELVA CENTRAL/POLITECNICO SELVA CENTRAL/POLITECNICO SELVA CENTRAL</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11476,6 +12846,16 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
+          <t>31537 - ASHANINGA/31537 - ASHANINGA/31537 - ASHANINGA</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11556,6 +12936,16 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
+          <t>LAS PALMAS/LAS PALMAS</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11636,6 +13026,16 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
+          <t>678 CASITA DE MONTESSORI</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11716,6 +13116,16 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
+          <t>QUITENI</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11796,6 +13206,16 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11876,6 +13296,16 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
+          <t>64551</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11956,6 +13386,16 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
+          <t>80023/80023</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12036,6 +13476,16 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
+          <t>80140 JOSE F. SANCHEZ CARRION/80140 JOSE F. SANCHEZ CARRION</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12116,6 +13566,16 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
+          <t>81585 SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12196,6 +13656,16 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
+          <t>81545/81545</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12276,6 +13746,16 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
+          <t>SAN JOSE</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12356,6 +13836,16 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
+          <t>80660</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12436,6 +13926,16 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
+          <t>1761 CLORINDA FLOR MARINA BEJARANO VALLEJO</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12516,6 +14016,16 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
+          <t>80099</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12596,6 +14106,16 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
+          <t>80889/80889</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12676,6 +14196,16 @@
       </c>
       <c r="T153" t="inlineStr">
         <is>
+          <t>80831 FRANCISCO BOLOGNESI/80831 FRANCISCO BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12756,6 +14286,16 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
+          <t>80649 CLODOMIRO MAGNO GUEVARA VARGAS/80649 CLODOMIRO MAGNO GUEVARA VARGAS/80649 CLODOMIRO MAGNO GUEVARA VARGAS</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12836,6 +14376,16 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12916,6 +14466,16 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
+          <t>81751 DIOS ES AMOR/81751 DIOS ES AMOR</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12996,6 +14556,16 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
+          <t>81607/81607/81607</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13076,6 +14646,16 @@
       </c>
       <c r="T158" t="inlineStr">
         <is>
+          <t>80794 ROGER RODRIGUEZ RODRIGUEZ/80794 ROGER RODRIGUEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13156,6 +14736,16 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
+          <t>80860 RICARDO PINILLOS MARTIN/80860 RICARDO PINILLOS MARTIN/80860 RICARDO PINILLOS MARTIN</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13236,6 +14826,16 @@
       </c>
       <c r="T160" t="inlineStr">
         <is>
+          <t>80038 SAN FRANCISCO DE ASIS/80038 SAN FRANCISCO DE ASIS/80038 SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13316,6 +14916,16 @@
       </c>
       <c r="T161" t="inlineStr">
         <is>
+          <t>80955</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13396,6 +15006,16 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
+          <t>JOSE ANTONIO GARCIA Y GARCIA</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13476,6 +15096,16 @@
       </c>
       <c r="T163" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13556,6 +15186,16 @@
       </c>
       <c r="T164" t="inlineStr">
         <is>
+          <t>10077/10077</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13636,6 +15276,16 @@
       </c>
       <c r="T165" t="inlineStr">
         <is>
+          <t>10143 CRISTO REY/10143 CRISTO REY</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13716,6 +15366,16 @@
       </c>
       <c r="T166" t="inlineStr">
         <is>
+          <t>CHONGOYAPE</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13796,6 +15456,16 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
+          <t>20849 JOSE FAUSTINO SANCHEZ CARRION</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13876,6 +15546,16 @@
       </c>
       <c r="T168" t="inlineStr">
         <is>
+          <t>62004 OLGA MANUELA DEL AGUILA ANGULO/62004 OLGA MANUELA DEL AGUILA ANGULO</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13956,6 +15636,16 @@
       </c>
       <c r="T169" t="inlineStr">
         <is>
+          <t>52129</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14036,6 +15726,16 @@
       </c>
       <c r="T170" t="inlineStr">
         <is>
+          <t>SAN PABLO</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14116,6 +15816,16 @@
       </c>
       <c r="T171" t="inlineStr">
         <is>
+          <t>EVARISTO SAN CRISTOBAL Y LEON</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14196,6 +15906,16 @@
       </c>
       <c r="T172" t="inlineStr">
         <is>
+          <t>TRECE DE MAYO</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14276,6 +15996,16 @@
       </c>
       <c r="T173" t="inlineStr">
         <is>
+          <t>14466 CESAR TRELLES LARA/14466 CESAR TRELLES LARA/14466 CESAR TRELLES LARA</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14356,6 +16086,16 @@
       </c>
       <c r="T174" t="inlineStr">
         <is>
+          <t>14457 ALEJANDRO ELERA LITUMA/14457 ALEJANDRO ELERA LITUMA/14457 ALEJANDRO ELERA LITUMA</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14436,6 +16176,16 @@
       </c>
       <c r="T175" t="inlineStr">
         <is>
+          <t>LUIS ALBERTO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14516,6 +16266,16 @@
       </c>
       <c r="T176" t="inlineStr">
         <is>
+          <t>15111/15111</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14596,6 +16356,16 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14676,6 +16446,16 @@
       </c>
       <c r="T178" t="inlineStr">
         <is>
+          <t>JUAN VELASCO ALVARADO/JUAN VELASCO ALVARADO/JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14756,6 +16536,16 @@
       </c>
       <c r="T179" t="inlineStr">
         <is>
+          <t>15026 FLORA CORDOVA DE TALLEDO/9 DE DICIEMBRE/9 DE DICIEMBRE/15026 FLORA CORDOVA DE TALLEDO</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14836,6 +16626,16 @@
       </c>
       <c r="T180" t="inlineStr">
         <is>
+          <t>14519/14519/14519</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14916,6 +16716,16 @@
       </c>
       <c r="T181" t="inlineStr">
         <is>
+          <t>14535</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14996,6 +16806,16 @@
       </c>
       <c r="T182" t="inlineStr">
         <is>
+          <t>20071</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15076,6 +16896,16 @@
       </c>
       <c r="T183" t="inlineStr">
         <is>
+          <t>MARISCAL CASTILLA</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15156,6 +16986,16 @@
       </c>
       <c r="T184" t="inlineStr">
         <is>
+          <t>15116</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15236,6 +17076,16 @@
       </c>
       <c r="T185" t="inlineStr">
         <is>
+          <t>72181 GLORIOSO 827/72181 GLORIOSO 827</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15316,6 +17166,16 @@
       </c>
       <c r="T186" t="inlineStr">
         <is>
+          <t>DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15396,6 +17256,16 @@
       </c>
       <c r="T187" t="inlineStr">
         <is>
+          <t>1228 NUEVA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15476,6 +17346,16 @@
       </c>
       <c r="T188" t="inlineStr">
         <is>
+          <t>70663 CARLOS DANTE NAVA SILVA</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15556,6 +17436,16 @@
       </c>
       <c r="T189" t="inlineStr">
         <is>
+          <t>71015 SAN JUAN BOSCO/71015 SAN JUAN BOSCO</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15636,6 +17526,16 @@
       </c>
       <c r="T190" t="inlineStr">
         <is>
+          <t>72002 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15716,6 +17616,16 @@
       </c>
       <c r="T191" t="inlineStr">
         <is>
+          <t>70400 VIRGEN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15796,6 +17706,16 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
+          <t>72004 VIRGEN DE FATIMA</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15876,6 +17796,16 @@
       </c>
       <c r="T193" t="inlineStr">
         <is>
+          <t>AGROPECUARIO UNTUCA</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15956,6 +17886,16 @@
       </c>
       <c r="T194" t="inlineStr">
         <is>
+          <t>BARRIO BELEN</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16036,6 +17976,16 @@
       </c>
       <c r="T195" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16116,6 +18066,16 @@
       </c>
       <c r="T196" t="inlineStr">
         <is>
+          <t>72073</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16196,6 +18156,16 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
+          <t>RICARDO PALMA</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16276,6 +18246,16 @@
       </c>
       <c r="T198" t="inlineStr">
         <is>
+          <t>TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16356,6 +18336,16 @@
       </c>
       <c r="T199" t="inlineStr">
         <is>
+          <t>70658</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16436,6 +18426,16 @@
       </c>
       <c r="T200" t="inlineStr">
         <is>
+          <t>194 CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16516,6 +18516,16 @@
       </c>
       <c r="T201" t="inlineStr">
         <is>
+          <t>CARLOS GUTIERREZ ZAMORA</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16596,6 +18606,16 @@
       </c>
       <c r="T202" t="inlineStr">
         <is>
+          <t>CARLOS OQUENDO DE AMAT</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16676,6 +18696,16 @@
       </c>
       <c r="T203" t="inlineStr">
         <is>
+          <t>TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16756,6 +18786,16 @@
       </c>
       <c r="T204" t="inlineStr">
         <is>
+          <t>70487 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16836,6 +18876,16 @@
       </c>
       <c r="T205" t="inlineStr">
         <is>
+          <t>PUCARA</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16916,6 +18966,16 @@
       </c>
       <c r="T206" t="inlineStr">
         <is>
+          <t>70394</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16996,6 +19056,16 @@
       </c>
       <c r="T207" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17076,6 +19146,16 @@
       </c>
       <c r="T208" t="inlineStr">
         <is>
+          <t>72908 JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17156,6 +19236,16 @@
       </c>
       <c r="T209" t="inlineStr">
         <is>
+          <t>72609 TUPAC AMARU II</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17236,6 +19326,16 @@
       </c>
       <c r="T210" t="inlineStr">
         <is>
+          <t>JOSE CARLOS MARIATEGUI/JOSE CARLOS MARIATEGUI/JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17316,6 +19416,16 @@
       </c>
       <c r="T211" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17396,6 +19506,16 @@
       </c>
       <c r="T212" t="inlineStr">
         <is>
+          <t>70492/70492</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17476,6 +19596,16 @@
       </c>
       <c r="T213" t="inlineStr">
         <is>
+          <t>HUATAQUITA</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17556,6 +19686,16 @@
       </c>
       <c r="T214" t="inlineStr">
         <is>
+          <t>72387</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17636,6 +19776,16 @@
       </c>
       <c r="T215" t="inlineStr">
         <is>
+          <t>SAN GABAN</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17716,6 +19866,16 @@
       </c>
       <c r="T216" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17796,6 +19956,16 @@
       </c>
       <c r="T217" t="inlineStr">
         <is>
+          <t>SAN MIGUEL/72442 GLORIOSO SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17876,6 +20046,16 @@
       </c>
       <c r="T218" t="inlineStr">
         <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17956,6 +20136,16 @@
       </c>
       <c r="T219" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18036,6 +20226,16 @@
       </c>
       <c r="T220" t="inlineStr">
         <is>
+          <t>72568/72568</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18116,6 +20316,16 @@
       </c>
       <c r="T221" t="inlineStr">
         <is>
+          <t>71007 MARIANO ZEVALLOS GONZALES</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18196,6 +20406,16 @@
       </c>
       <c r="T222" t="inlineStr">
         <is>
+          <t>RETOÑITOS</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18276,6 +20496,16 @@
       </c>
       <c r="T223" t="inlineStr">
         <is>
+          <t>MICAELA BASTIDAS</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18356,6 +20586,16 @@
       </c>
       <c r="T224" t="inlineStr">
         <is>
+          <t>DIVINO MAESTRO</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18436,6 +20676,16 @@
       </c>
       <c r="T225" t="inlineStr">
         <is>
+          <t>0271/0271</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18516,6 +20766,16 @@
       </c>
       <c r="T226" t="inlineStr">
         <is>
+          <t>0633/0633</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18596,6 +20856,16 @@
       </c>
       <c r="T227" t="inlineStr">
         <is>
+          <t>0588 JUAN GUILLERMO CASTILLO DELGADO/0588 JUAN GUILLERMO CASTILLO DELGADO/0588 JUAN GUILLERMO CASTILLO DELGADO</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18676,6 +20946,16 @@
       </c>
       <c r="T228" t="inlineStr">
         <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18756,6 +21036,16 @@
       </c>
       <c r="T229" t="inlineStr">
         <is>
+          <t>0700 SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18836,6 +21126,16 @@
       </c>
       <c r="T230" t="inlineStr">
         <is>
+          <t>0240/0240</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18916,6 +21216,16 @@
       </c>
       <c r="T231" t="inlineStr">
         <is>
+          <t>0184 OSCAR PANDURO DAVILA</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18996,6 +21306,16 @@
       </c>
       <c r="T232" t="inlineStr">
         <is>
+          <t>0230/0230/0230</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19076,6 +21396,16 @@
       </c>
       <c r="T233" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19156,6 +21486,16 @@
       </c>
       <c r="T234" t="inlineStr">
         <is>
+          <t>120 MI MUNDO MAGICO</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19236,6 +21576,16 @@
       </c>
       <c r="T235" t="inlineStr">
         <is>
+          <t>JOSE ANTONIO ENCINAS FRANCO/JOSE ANTONIO ENCINAS FRANCO/JOSE ANTONIO ENCINAS FRANCO</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19316,6 +21666,16 @@
       </c>
       <c r="T236" t="inlineStr">
         <is>
+          <t>INCA GARCILASO DE LA VEGA/INCA GARCILASO DE LA VEGA/INCA GARCILASO DE LA VEGA/INCA GARCILASO DE LA VEGA</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19396,6 +21756,16 @@
       </c>
       <c r="T237" t="inlineStr">
         <is>
+          <t>34432</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19476,6 +21846,16 @@
       </c>
       <c r="T238" t="inlineStr">
         <is>
+          <t>32603/32603</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19556,6 +21936,16 @@
       </c>
       <c r="T239" t="inlineStr">
         <is>
+          <t>54200</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19636,6 +22026,16 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
+          <t>54199</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19716,6 +22116,16 @@
       </c>
       <c r="T241" t="inlineStr">
         <is>
+          <t>SANTO TORIBIO/SANTO TORIBIO/SANTO TORIBIO/SANTO TORIBIO</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19796,6 +22206,16 @@
       </c>
       <c r="T242" t="inlineStr">
         <is>
+          <t>1179</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19876,6 +22296,16 @@
       </c>
       <c r="T243" t="inlineStr">
         <is>
+          <t>80608</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19956,6 +22386,16 @@
       </c>
       <c r="T244" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20036,6 +22476,16 @@
       </c>
       <c r="T245" t="inlineStr">
         <is>
+          <t>38984-18 JOSE ABEL ALFARO PACHECO/38984-18 JOSE ABEL ALFARO PACHECO</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20116,6 +22566,16 @@
       </c>
       <c r="T246" t="inlineStr">
         <is>
+          <t>10411/10411</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20196,6 +22656,16 @@
       </c>
       <c r="T247" t="inlineStr">
         <is>
+          <t>80085 MIGUEL GRAU SEMINARIO/80085 MIGUEL GRAU SEMINARIO</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20276,6 +22746,16 @@
       </c>
       <c r="T248" t="inlineStr">
         <is>
+          <t>103 SAGRADO CORAZON DE MARIA/103 SAGRADO CORAZON DE MARIA</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20356,6 +22836,16 @@
       </c>
       <c r="T249" t="inlineStr">
         <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20436,6 +22926,16 @@
       </c>
       <c r="T250" t="inlineStr">
         <is>
+          <t>11207 JESUS PEREGRINO DE PAZ</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20516,6 +23016,16 @@
       </c>
       <c r="T251" t="inlineStr">
         <is>
+          <t>432-124</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20596,6 +23106,16 @@
       </c>
       <c r="T252" t="inlineStr">
         <is>
+          <t>2339</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20676,6 +23196,16 @@
       </c>
       <c r="T253" t="inlineStr">
         <is>
+          <t>80052 MICAELA BASTIDAS/80052 MICAELA BASTIDAS</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20756,6 +23286,16 @@
       </c>
       <c r="T254" t="inlineStr">
         <is>
+          <t>17786 FERNANDO BELAUNDE TERRY/17786 FERNANDO BELAUNDE TERRY/17786 FERNANDO BELAUNDE TERRY</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20836,6 +23376,16 @@
       </c>
       <c r="T255" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20916,6 +23466,16 @@
       </c>
       <c r="T256" t="inlineStr">
         <is>
+          <t>32775</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20996,6 +23556,16 @@
       </c>
       <c r="T257" t="inlineStr">
         <is>
+          <t>30283 SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21076,6 +23646,16 @@
       </c>
       <c r="T258" t="inlineStr">
         <is>
+          <t>24379</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21156,6 +23736,16 @@
       </c>
       <c r="T259" t="inlineStr">
         <is>
+          <t>SAN JUAN DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21236,6 +23826,16 @@
       </c>
       <c r="T260" t="inlineStr">
         <is>
+          <t>SIMON BOLIVAR/SIMON BOLIVAR/OTUZCO</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21316,6 +23916,16 @@
       </c>
       <c r="T261" t="inlineStr">
         <is>
+          <t>16004</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21396,6 +24006,16 @@
       </c>
       <c r="T262" t="inlineStr">
         <is>
+          <t>14906 CRISTO REY</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21476,6 +24096,16 @@
       </c>
       <c r="T263" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21556,6 +24186,16 @@
       </c>
       <c r="T264" t="inlineStr">
         <is>
+          <t>70583 PEDRO VILCAPAZA</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21636,6 +24276,16 @@
       </c>
       <c r="T265" t="inlineStr">
         <is>
+          <t>80955/80955</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21716,6 +24366,16 @@
       </c>
       <c r="T266" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21796,6 +24456,16 @@
       </c>
       <c r="T267" t="inlineStr">
         <is>
+          <t>0414/0414/0414</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21876,6 +24546,16 @@
       </c>
       <c r="T268" t="inlineStr">
         <is>
+          <t>CARLOS ISMAEL NORIEGA JIMENEZ</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21956,6 +24636,16 @@
       </c>
       <c r="T269" t="inlineStr">
         <is>
+          <t>22039</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22036,6 +24726,16 @@
       </c>
       <c r="T270" t="inlineStr">
         <is>
+          <t>CORONEL FRANCISCO BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22116,6 +24816,16 @@
       </c>
       <c r="T271" t="inlineStr">
         <is>
+          <t>24243 PORTAL DEL VALLE HUANCA HUANCA</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22196,6 +24906,16 @@
       </c>
       <c r="T272" t="inlineStr">
         <is>
+          <t>00550</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22276,6 +24996,16 @@
       </c>
       <c r="T273" t="inlineStr">
         <is>
+          <t>38638</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22356,6 +25086,16 @@
       </c>
       <c r="T274" t="inlineStr">
         <is>
+          <t>MARISCAL RAMON CASTILLA/MARISCAL RAMON CASTILLA</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22436,6 +25176,16 @@
       </c>
       <c r="T275" t="inlineStr">
         <is>
+          <t>56430</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22516,6 +25266,16 @@
       </c>
       <c r="T276" t="inlineStr">
         <is>
+          <t>14429 RICARDO HUMBERTO RAMOS PLATA/14429 RICARDO HUMBERTO RAMOS PLATA/14429 RICARDO HUMBERTO RAMOS PLATA</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22596,6 +25356,16 @@
       </c>
       <c r="T277" t="inlineStr">
         <is>
+          <t>33399</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22676,6 +25446,16 @@
       </c>
       <c r="T278" t="inlineStr">
         <is>
+          <t>158 VIRGEN ASUNTA</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22756,6 +25536,16 @@
       </c>
       <c r="T279" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22836,6 +25626,16 @@
       </c>
       <c r="T280" t="inlineStr">
         <is>
+          <t>SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22916,6 +25716,16 @@
       </c>
       <c r="T281" t="inlineStr">
         <is>
+          <t>JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22996,6 +25806,16 @@
       </c>
       <c r="T282" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23076,6 +25896,16 @@
       </c>
       <c r="T283" t="inlineStr">
         <is>
+          <t>0771 JOSE FAUSTINO SANCHEZ CARRION/0771 JOSE FAUSTINO SANCHEZ CARRION/0771 JOSE FAUSTINO SANCHEZ CARRION</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23156,6 +25986,16 @@
       </c>
       <c r="T284" t="inlineStr">
         <is>
+          <t>JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23236,6 +26076,16 @@
       </c>
       <c r="T285" t="inlineStr">
         <is>
+          <t>31279</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23316,6 +26166,16 @@
       </c>
       <c r="T286" t="inlineStr">
         <is>
+          <t>86309 FLAVIO MAXIMO VEGA VILLANUEVA/86309 FLAVIO MAXIMO VEGA VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23396,6 +26256,16 @@
       </c>
       <c r="T287" t="inlineStr">
         <is>
+          <t>32073/32073</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23476,6 +26346,16 @@
       </c>
       <c r="T288" t="inlineStr">
         <is>
+          <t>31774 SAN ANDRES/31774 SAN ANDRES DE PARAGSHA/31774 SAN ANDRES</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23556,6 +26436,16 @@
       </c>
       <c r="T289" t="inlineStr">
         <is>
+          <t>30179 MARIA AUXILIADORA</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23636,6 +26526,16 @@
       </c>
       <c r="T290" t="inlineStr">
         <is>
+          <t>16523/16523</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23716,6 +26616,16 @@
       </c>
       <c r="T291" t="inlineStr">
         <is>
+          <t>CAMINACA</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23796,6 +26706,16 @@
       </c>
       <c r="T292" t="inlineStr">
         <is>
+          <t>0195/0195</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23876,6 +26796,16 @@
       </c>
       <c r="T293" t="inlineStr">
         <is>
+          <t>GERMAN CARO RIOS</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23956,6 +26886,16 @@
       </c>
       <c r="T294" t="inlineStr">
         <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24036,6 +26976,16 @@
       </c>
       <c r="T295" t="inlineStr">
         <is>
+          <t>32914</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24116,6 +27066,16 @@
       </c>
       <c r="T296" t="inlineStr">
         <is>
+          <t>32547</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24196,6 +27156,16 @@
       </c>
       <c r="T297" t="inlineStr">
         <is>
+          <t>SAN ANTONIO DE JEBERILLOS/SAN ANTONIO DE JEBERILLOS</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24276,6 +27246,16 @@
       </c>
       <c r="T298" t="inlineStr">
         <is>
+          <t>80992/80992/80992</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24356,6 +27336,16 @@
       </c>
       <c r="T299" t="inlineStr">
         <is>
+          <t>18282</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24436,6 +27426,16 @@
       </c>
       <c r="T300" t="inlineStr">
         <is>
+          <t>38761 LIBERTADORES DEL VRAE/38761 LIBERTADORES DEL VRAE/38761 LIBERTADORES DEL VRAE</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24516,6 +27516,16 @@
       </c>
       <c r="T301" t="inlineStr">
         <is>
+          <t>SAN JUAN</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24596,6 +27606,16 @@
       </c>
       <c r="T302" t="inlineStr">
         <is>
+          <t>54080</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24676,6 +27696,16 @@
       </c>
       <c r="T303" t="inlineStr">
         <is>
+          <t>10650</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24756,6 +27786,16 @@
       </c>
       <c r="T304" t="inlineStr">
         <is>
+          <t>CCORICHICHINA</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24836,6 +27876,16 @@
       </c>
       <c r="T305" t="inlineStr">
         <is>
+          <t>56258/56258</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24916,6 +27966,16 @@
       </c>
       <c r="T306" t="inlineStr">
         <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24996,6 +28056,16 @@
       </c>
       <c r="T307" t="inlineStr">
         <is>
+          <t>0206 ISAAC NEWTON/0206 ISAAC NEWTON</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25076,6 +28146,16 @@
       </c>
       <c r="T308" t="inlineStr">
         <is>
+          <t>JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25156,6 +28236,16 @@
       </c>
       <c r="T309" t="inlineStr">
         <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25236,6 +28326,16 @@
       </c>
       <c r="T310" t="inlineStr">
         <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25316,6 +28416,16 @@
       </c>
       <c r="T311" t="inlineStr">
         <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25396,6 +28506,16 @@
       </c>
       <c r="T312" t="inlineStr">
         <is>
+          <t>56394 CESAR VALLEJO/56394 CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25476,6 +28596,16 @@
       </c>
       <c r="T313" t="inlineStr">
         <is>
+          <t>56207 RICARDO PALMA SORIANO/56207 RICARDO PALMA SORIANO</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25556,6 +28686,16 @@
       </c>
       <c r="T314" t="inlineStr">
         <is>
+          <t>0448 HECTOR SAAVEDRA DEL CASTILLO/0448 HECTOR SAAVEDRA DEL CASTILLO</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25636,6 +28776,16 @@
       </c>
       <c r="T315" t="inlineStr">
         <is>
+          <t>30935/30935</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25716,6 +28866,16 @@
       </c>
       <c r="T316" t="inlineStr">
         <is>
+          <t>34031 13 DE AGOSTO/13 DE AGOSTO/13 DE AGOSTO</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25796,6 +28956,16 @@
       </c>
       <c r="T317" t="inlineStr">
         <is>
+          <t>72619</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25876,6 +29046,16 @@
       </c>
       <c r="T318" t="inlineStr">
         <is>
+          <t>SIERVOS DE DIOS</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25956,6 +29136,16 @@
       </c>
       <c r="T319" t="inlineStr">
         <is>
+          <t>72128</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26036,6 +29226,16 @@
       </c>
       <c r="T320" t="inlineStr">
         <is>
+          <t>MUÑANI</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26116,6 +29316,16 @@
       </c>
       <c r="T321" t="inlineStr">
         <is>
+          <t>86628 CAPITAN FAP JOSE ABELARDO QUIÑONES</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26196,6 +29406,16 @@
       </c>
       <c r="T322" t="inlineStr">
         <is>
+          <t>50593</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26276,6 +29496,16 @@
       </c>
       <c r="T323" t="inlineStr">
         <is>
+          <t>SAN PEDRO</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26356,6 +29586,16 @@
       </c>
       <c r="T324" t="inlineStr">
         <is>
+          <t>86253 CELSO GARRO VALDERRAMA/86253 CELSO GARRO VALDERRAMA</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26436,6 +29676,16 @@
       </c>
       <c r="T325" t="inlineStr">
         <is>
+          <t>MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26516,6 +29766,16 @@
       </c>
       <c r="T326" t="inlineStr">
         <is>
+          <t>16536 SAN MIGUEL/16536 SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26596,6 +29856,16 @@
       </c>
       <c r="T327" t="inlineStr">
         <is>
+          <t>80161/80161</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26676,6 +29946,16 @@
       </c>
       <c r="T328" t="inlineStr">
         <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26756,6 +30036,16 @@
       </c>
       <c r="T329" t="inlineStr">
         <is>
+          <t>70618</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26836,6 +30126,16 @@
       </c>
       <c r="T330" t="inlineStr">
         <is>
+          <t>LA INMACULADA/LA INMACULADA/LA INMACULADA</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26916,6 +30216,16 @@
       </c>
       <c r="T331" t="inlineStr">
         <is>
+          <t>AMALIA CAMPOS DE BELEVAN</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26996,6 +30306,16 @@
       </c>
       <c r="T332" t="inlineStr">
         <is>
+          <t>MICAELA BASTIDAS</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27076,6 +30396,16 @@
       </c>
       <c r="T333" t="inlineStr">
         <is>
+          <t>0138 JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27156,6 +30486,16 @@
       </c>
       <c r="T334" t="inlineStr">
         <is>
+          <t>00937 DAVID BOCANEGRA VASQUEZ</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27236,6 +30576,16 @@
       </c>
       <c r="T335" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27316,6 +30666,16 @@
       </c>
       <c r="T336" t="inlineStr">
         <is>
+          <t>10421</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27396,6 +30756,16 @@
       </c>
       <c r="T337" t="inlineStr">
         <is>
+          <t>SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27476,6 +30846,16 @@
       </c>
       <c r="T338" t="inlineStr">
         <is>
+          <t>00533</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27556,6 +30936,16 @@
       </c>
       <c r="T339" t="inlineStr">
         <is>
+          <t>VICENTE MERINO SAAVEDRA/VICENTE MERINO SAAVEDRA</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27636,6 +31026,16 @@
       </c>
       <c r="T340" t="inlineStr">
         <is>
+          <t>JORGE BASADRE</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27716,6 +31116,16 @@
       </c>
       <c r="T341" t="inlineStr">
         <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27796,6 +31206,16 @@
       </c>
       <c r="T342" t="inlineStr">
         <is>
+          <t>18203</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27876,6 +31296,16 @@
       </c>
       <c r="T343" t="inlineStr">
         <is>
+          <t>88162/88162</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27956,6 +31386,16 @@
       </c>
       <c r="T344" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28036,6 +31476,16 @@
       </c>
       <c r="T345" t="inlineStr">
         <is>
+          <t>40074 JOSE L. BUSTAMANTE Y RIVERO/40074 JOSE L. BUSTAMANTE Y RIVERO</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28116,6 +31566,16 @@
       </c>
       <c r="T346" t="inlineStr">
         <is>
+          <t>40157 JORGE LUIS BORGES</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28196,6 +31656,16 @@
       </c>
       <c r="T347" t="inlineStr">
         <is>
+          <t>432-159</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28276,6 +31746,16 @@
       </c>
       <c r="T348" t="inlineStr">
         <is>
+          <t>PIO PACHECO CANDIA</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28356,6 +31836,16 @@
       </c>
       <c r="T349" t="inlineStr">
         <is>
+          <t>16959</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28436,6 +31926,16 @@
       </c>
       <c r="T350" t="inlineStr">
         <is>
+          <t>ANTERO EFRAIN UGARTE VIZCARRA</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28516,6 +32016,16 @@
       </c>
       <c r="T351" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28596,6 +32106,16 @@
       </c>
       <c r="T352" t="inlineStr">
         <is>
+          <t>501447 YAWARMAYO</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28676,6 +32196,16 @@
       </c>
       <c r="T353" t="inlineStr">
         <is>
+          <t>50497/ROSA DE AMERICA</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28756,6 +32286,16 @@
       </c>
       <c r="T354" t="inlineStr">
         <is>
+          <t>56326/56326/56326</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28836,6 +32376,16 @@
       </c>
       <c r="T355" t="inlineStr">
         <is>
+          <t>32123 JOSE ANTONIO ENCINAS FRANCO/32123</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28916,6 +32466,16 @@
       </c>
       <c r="T356" t="inlineStr">
         <is>
+          <t>32418/32418/32418</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28996,6 +32556,16 @@
       </c>
       <c r="T357" t="inlineStr">
         <is>
+          <t>32217/32217/32217</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29076,6 +32646,16 @@
       </c>
       <c r="T358" t="inlineStr">
         <is>
+          <t>PEDRO GALVEZ EGUSQUIZA/PEDRO GALVEZ EGUSQUIZA/PEDRO GALVEZ EGUSQUIZA</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29156,6 +32736,16 @@
       </c>
       <c r="T359" t="inlineStr">
         <is>
+          <t>32289/32289/32289</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29236,6 +32826,16 @@
       </c>
       <c r="T360" t="inlineStr">
         <is>
+          <t>32550</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29316,6 +32916,16 @@
       </c>
       <c r="T361" t="inlineStr">
         <is>
+          <t>32495 HANS VICTOR LANGEMAK MICHELSEN/32495 HANS VICTOR LANGEMAK MICHELSEN</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29396,6 +33006,16 @@
       </c>
       <c r="T362" t="inlineStr">
         <is>
+          <t>32132/32132</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29476,6 +33096,16 @@
       </c>
       <c r="T363" t="inlineStr">
         <is>
+          <t>80893 NUESTRA SEÑORA DE LA CANDELARIA/80893 NUESTRA SEÑORA DE LA CANDELARIA</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29556,6 +33186,16 @@
       </c>
       <c r="T364" t="inlineStr">
         <is>
+          <t>20504 SAN JERONIMO/20504 SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29636,6 +33276,16 @@
       </c>
       <c r="T365" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29716,6 +33366,16 @@
       </c>
       <c r="T366" t="inlineStr">
         <is>
+          <t>14601/14601/14601</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29796,6 +33456,16 @@
       </c>
       <c r="T367" t="inlineStr">
         <is>
+          <t>20145/20145</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29876,6 +33546,16 @@
       </c>
       <c r="T368" t="inlineStr">
         <is>
+          <t>20035/20035</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29956,6 +33636,16 @@
       </c>
       <c r="T369" t="inlineStr">
         <is>
+          <t>70394</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30036,6 +33726,16 @@
       </c>
       <c r="T370" t="inlineStr">
         <is>
+          <t>72074</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30116,6 +33816,16 @@
       </c>
       <c r="T371" t="inlineStr">
         <is>
+          <t>72073</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30196,6 +33906,16 @@
       </c>
       <c r="T372" t="inlineStr">
         <is>
+          <t>JUAN VELAZCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30276,6 +33996,16 @@
       </c>
       <c r="T373" t="inlineStr">
         <is>
+          <t>CAMINACA</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30356,6 +34086,16 @@
       </c>
       <c r="T374" t="inlineStr">
         <is>
+          <t>70258</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30436,6 +34176,16 @@
       </c>
       <c r="T375" t="inlineStr">
         <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30516,6 +34266,16 @@
       </c>
       <c r="T376" t="inlineStr">
         <is>
+          <t>72128</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30596,6 +34356,16 @@
       </c>
       <c r="T377" t="inlineStr">
         <is>
+          <t>0800/0800</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30676,6 +34446,16 @@
       </c>
       <c r="T378" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30756,6 +34536,16 @@
       </c>
       <c r="T379" t="inlineStr">
         <is>
+          <t>DIONISIO OCAMPO CHAVEZ/00518 DIONISIO OCAMPO CHAVEZ</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30836,6 +34626,16 @@
       </c>
       <c r="T380" t="inlineStr">
         <is>
+          <t>0759 FRANCISCO BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30916,6 +34716,16 @@
       </c>
       <c r="T381" t="inlineStr">
         <is>
+          <t>64691</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30996,6 +34806,16 @@
       </c>
       <c r="T382" t="inlineStr">
         <is>
+          <t>MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31076,6 +34896,16 @@
       </c>
       <c r="T383" t="inlineStr">
         <is>
+          <t>86104 AUGUSTO ALBA HERRERA/86104 AUGUSTO ALBA HERRERA</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31156,6 +34986,16 @@
       </c>
       <c r="T384" t="inlineStr">
         <is>
+          <t>54113 JOSE MARIA ARGUEDAS</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31236,6 +35076,16 @@
       </c>
       <c r="T385" t="inlineStr">
         <is>
+          <t>40207 MARIANO MELGAR VALDIVIESO</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31316,6 +35166,16 @@
       </c>
       <c r="T386" t="inlineStr">
         <is>
+          <t>300 LOS NIÑOS DE FATIMA</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31396,6 +35256,16 @@
       </c>
       <c r="T387" t="inlineStr">
         <is>
+          <t>JUAN PABLO II</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31476,6 +35346,16 @@
       </c>
       <c r="T388" t="inlineStr">
         <is>
+          <t>50123 SAN LUIS GONZAGA/50123 SAN LUIS GONZAGA/50123 SAN LUIS GONZAGA</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31556,6 +35436,16 @@
       </c>
       <c r="T389" t="inlineStr">
         <is>
+          <t>436 SAN NICOLAS DE BARI</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31636,6 +35526,16 @@
       </c>
       <c r="T390" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31716,6 +35616,16 @@
       </c>
       <c r="T391" t="inlineStr">
         <is>
+          <t>JOSE GABRIEL CONDORCANQUI</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31796,6 +35706,16 @@
       </c>
       <c r="T392" t="inlineStr">
         <is>
+          <t>SEÑOR JUSTO JUEZ</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31876,6 +35796,16 @@
       </c>
       <c r="T393" t="inlineStr">
         <is>
+          <t>ANTONIO BRACK EGG</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31956,6 +35886,16 @@
       </c>
       <c r="T394" t="inlineStr">
         <is>
+          <t>22615</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32036,6 +35976,16 @@
       </c>
       <c r="T395" t="inlineStr">
         <is>
+          <t>CORONEL LEONCIO PRADO GUTIERREZ/CORONEL LEONCIO PRADO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32116,6 +36066,16 @@
       </c>
       <c r="T396" t="inlineStr">
         <is>
+          <t>22681</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32196,6 +36156,16 @@
       </c>
       <c r="T397" t="inlineStr">
         <is>
+          <t>20795 CESAR ABRAHAM VALLEJO MENDOZA/20795 CESAR ABRAHAM VALLEJO MENDOZA/20795 CESAR ABRAHAM VALLEJO MENDOZA/20795 CESAR ABRAHAM VALLEJO MENDOZA/20795 CESAR ABRAHAM VALLEJO MENDOZA</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32276,6 +36246,16 @@
       </c>
       <c r="T398" t="inlineStr">
         <is>
+          <t>DIONISIO MANCO CAMPOS/DIONISIO MANCO CAMPOS/DIONISIO MANCO CAMPOS</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32356,6 +36336,16 @@
       </c>
       <c r="T399" t="inlineStr">
         <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32436,6 +36426,16 @@
       </c>
       <c r="T400" t="inlineStr">
         <is>
+          <t>6 DE DICIEMBRE/6 DE DICIEMBRE/34002 6 DE DICIEMBRE</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V400" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32516,6 +36516,16 @@
       </c>
       <c r="T401" t="inlineStr">
         <is>
+          <t>14761/14761</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32596,6 +36606,16 @@
       </c>
       <c r="T402" t="inlineStr">
         <is>
+          <t>CRISTO REY/CRISTO REY</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32676,6 +36696,16 @@
       </c>
       <c r="T403" t="inlineStr">
         <is>
+          <t>SAN JOSE</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V403" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32756,6 +36786,16 @@
       </c>
       <c r="T404" t="inlineStr">
         <is>
+          <t>20042</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V404" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32836,6 +36876,16 @@
       </c>
       <c r="T405" t="inlineStr">
         <is>
+          <t>ELOY ALADINO PINTADO LIMA/ELOY ALADINO PINTADO LIMA/ELOY ALADINO PINTADO LIMA</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32916,6 +36966,16 @@
       </c>
       <c r="T406" t="inlineStr">
         <is>
+          <t>72182 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V406" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32996,6 +37056,16 @@
       </c>
       <c r="T407" t="inlineStr">
         <is>
+          <t>BARRIO BELEN</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33076,6 +37146,16 @@
       </c>
       <c r="T408" t="inlineStr">
         <is>
+          <t>70502 GENERAL PEDRO VILCA APAZA</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33156,6 +37236,16 @@
       </c>
       <c r="T409" t="inlineStr">
         <is>
+          <t>ISIVILLA</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33236,6 +37326,16 @@
       </c>
       <c r="T410" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33316,6 +37416,16 @@
       </c>
       <c r="T411" t="inlineStr">
         <is>
+          <t>70075</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33396,6 +37506,16 @@
       </c>
       <c r="T412" t="inlineStr">
         <is>
+          <t>PUSI</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33476,6 +37596,16 @@
       </c>
       <c r="T413" t="inlineStr">
         <is>
+          <t>MUNI</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33556,6 +37686,16 @@
       </c>
       <c r="T414" t="inlineStr">
         <is>
+          <t>70635 HORACIO ZEBALLOS GAMEZ</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33636,6 +37776,16 @@
       </c>
       <c r="T415" t="inlineStr">
         <is>
+          <t>00622/00622</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V415" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33716,6 +37866,16 @@
       </c>
       <c r="T416" t="inlineStr">
         <is>
+          <t>0438 FERNANDO BELAUNDE TERRY</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33796,6 +37956,16 @@
       </c>
       <c r="T417" t="inlineStr">
         <is>
+          <t>00912/00912</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33876,6 +38046,16 @@
       </c>
       <c r="T418" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33956,6 +38136,16 @@
       </c>
       <c r="T419" t="inlineStr">
         <is>
+          <t>035 HORACIO ZEVALLOS GAMEZ/035 HORACIO ZEVALLOS GAMEZ</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>

--- a/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_ugsc_asitec.xlsx
+++ b/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_ugsc_asitec.xlsx
@@ -419,57 +419,57 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CUI</t>
+          <t>cui</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Cantidad de locales educativos intervenidos por el PI</t>
+          <t>cantidad_de_locales_educativos_intervenidos_por_el_pi</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Periodo inicial</t>
+          <t>periodo_inicial</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Periodo final / actual</t>
+          <t>periodo_final_actual</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Monto de inversión (S/)</t>
+          <t>monto</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Estado (Admitido, Continuidad, Culminado, Descalificado, Desestimado, En Revisión, Revisado, etc.)</t>
+          <t>estado_admitido_continuidad_culminado_descalificado_desestim</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Etapa (Costos, Culminado, Especialidades, Estudios Básicos, No Culminado, Revisado, etc.)</t>
+          <t>etapa_costos_culminado_especialidades_estudios_basicos_no_cu</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Fecha de aprobación del Expediente Técnico (ET) (estimado)</t>
+          <t>fecha_de_aprobacion_del_expediente_tecnico_et_estimado</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Fecha de caducidad del ET</t>
+          <t>fecha_de_caducidad_del_et</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
